--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>100.6736145019531</v>
+      </c>
+      <c r="G56" t="n">
+        <v>101.6800003051758</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.006385803222685</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9897578680194564</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6552340623829631</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>101.4806976318359</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>101.551758,101.556938,101.493881,101.559296,101.438248,101.445770,101.394836,101.326973,101.285286,101.223007,101.143845,101.152176,101.101730,101.012505,101.031540,100.915871,100.962578,100.954422,100.907974,100.788704,100.799408,100.794807,100.665947,100.673615</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>101.639999,101.680000,101.650002,101.820000,101.980003,102.120003,102.110001,102.029999,101.949997,101.980003,102.040001,102.059998,101.930000,101.629997,101.260002,101.339996,101.470001,101.650002,101.739998,101.709999,102.250000,101.879997,101.599998,101.680000</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.088241,0.123062,0.156121,0.260704,0.541755,0.674233,0.715165,0.703026,0.664711,0.756996,0.896156,0.907822,0.828270,0.617492,0.228462,0.424125,0.507423,0.695580,0.832024,0.921295,1.450592,1.085190,0.934051,1.006385</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.086818,0.121029,0.153586,0.256044,0.531237,0.660236,0.700386,0.689038,0.651997,0.742299,0.878240,0.889498,0.812587,0.607589,0.225619,0.418517,0.500072,0.684289,0.817794,0.905806,1.418672,1.065165,0.919342,0.989757</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6552340623829631</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>101.345901,101.325012,101.620415,101.474876,101.454308,101.403008,101.221085,101.387627,101.014206,101.344254,101.171364,101.225151,100.906563,101.072052,101.177856,100.737900,100.894615,100.936356,100.810280,100.682236,100.767876,100.723534,100.670563,100.664749</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>101.064529,100.918495,100.711418,100.733192,100.478699,100.321075,100.174301,100.073166,100.120506,99.914787,99.655624,99.587959,99.564705,99.333130,99.422920,99.324951,99.127144,99.013550,98.888214,98.823105,98.855698,98.654495,98.601288,98.544571</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>101.704399,101.685150,101.595993,101.675201,101.606705,101.687805,101.661407,101.586464,101.632538,101.664497,101.576202,101.607872,101.595421,101.507652,101.554214,101.611923,101.580681,101.534142,101.506714,101.516113,101.550499,101.495422,101.502045,101.480698</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>101.592354,101.585670,101.668144,101.676003,101.844887,101.528618,101.741882,101.584389,101.487000,101.685928,101.577621,101.576172,101.541908,101.633911,101.496696,101.556061,101.613861,101.581146,101.626770,101.464737,101.439560,101.512115,101.559799,101.421494</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>101.011040,100.998810,100.687119,100.714157,100.629524,100.573929,100.433517,100.245331,100.100616,100.068649,99.834000,99.753822,99.649063,99.502014,99.479630,99.486603,99.327637,99.311554,98.965790,98.891472,98.899719,98.905762,98.862030,98.666588</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>101.367363,101.266022,101.083145,101.110779,100.967484,100.924973,100.870850,100.809822,100.823586,100.783493,100.458717,100.497597,100.517113,100.257057,100.273376,100.380356,100.165688,100.129684,100.017365,100.048447,100.055870,99.870422,99.918709,99.832985</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>101.4806976318359</v>
+      </c>
+      <c r="G57" t="n">
+        <v>101.0400009155273</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.4406967163085511</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4361606416423013</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.108174688274574</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:32</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>100.8107147216797</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>101.704399,101.685150,101.595993,101.675201,101.606705,101.687805,101.661407,101.586464,101.632538,101.664497,101.576202,101.607872,101.595421,101.507652,101.554214,101.611923,101.580681,101.534142,101.506714,101.516113,101.550499,101.495422,101.502045,101.480698</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>101.790001,101.220001,100.690002,99.970001,99.830002,99.519997,99.790001,99.690002,100.080002,100.639999,100.209999,100.790001,100.970001,101.180000,100.919998,101.440002,101.320000,99.690002,99.250000,99.629997,100.120003,100.959999,100.940002,101.040001</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.085602,0.465149,0.905991,1.705200,1.776703,2.167808,1.871406,1.896462,1.552536,1.024498,1.366203,0.817871,0.625420,0.327652,0.634216,0.171921,0.260681,1.844140,2.256714,1.886116,1.430496,0.535423,0.562043,0.440697</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.084097,0.459542,0.899782,1.705711,1.779729,2.178264,1.875344,1.902359,1.551295,1.017983,1.363340,0.811461,0.619411,0.323830,0.628434,0.169480,0.257285,1.849874,2.273767,1.893120,1.428782,0.530332,0.556809,0.436161</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1.108174688274574</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>101.592354,101.585670,101.668144,101.676003,101.844887,101.528618,101.741882,101.584389,101.487000,101.685928,101.577621,101.576172,101.541908,101.633911,101.496696,101.556061,101.613861,101.581146,101.626770,101.464737,101.439560,101.512115,101.559799,101.421494</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>101.367363,101.266022,101.083145,101.110779,100.967484,100.924973,100.870850,100.809822,100.823586,100.783493,100.458717,100.497597,100.517113,100.257057,100.273376,100.380356,100.165688,100.129684,100.017365,100.048447,100.055870,99.870422,99.918709,99.832985</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:32</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100.945442,100.919884,100.851273,100.865845,100.792946,100.769943,100.772568,100.736382,100.758568,100.800476,100.780342,100.821022,100.858109,100.801910,100.847916,100.850533,100.822311,100.793449,100.812637,100.813416,100.834557,100.742401,100.788132,100.810715</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>100.803040,100.856689,100.938263,100.805748,101.009712,100.765854,100.892487,100.817421,100.737198,100.922012,100.904221,100.843208,100.901993,100.916206,100.975395,100.729980,100.811867,100.926453,101.151550,100.800613,100.757828,100.803467,100.956528,100.926338</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>100.155083,100.055344,99.805710,99.778328,99.604881,99.449150,99.434975,99.286064,99.144760,99.143845,99.082100,99.045876,98.987083,98.910378,98.963905,98.925453,98.757843,98.789703,98.439766,98.371140,98.423897,98.409981,98.402451,98.230461</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>100.518082,100.372314,100.188591,100.154160,100.033348,99.837189,99.881798,99.830025,99.874664,99.773628,99.627068,99.670845,99.726784,99.552200,99.693390,99.733788,99.485649,99.445702,99.366356,99.404358,99.421776,99.182465,99.269409,99.103477</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>100.8107147216797</v>
+      </c>
+      <c r="G58" t="n">
+        <v>101.2099990844727</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3992843627929545</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.3945107858954734</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.280075530736436</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>101.0064926147461</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>100.945442,100.919884,100.851273,100.865845,100.792946,100.769943,100.772568,100.736382,100.758568,100.800476,100.780342,100.821022,100.858109,100.801910,100.847916,100.850533,100.822311,100.793449,100.812637,100.813416,100.834557,100.742401,100.788132,100.810715</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>101.050003,101.500000,101.559998,101.459999,101.900002,101.730003,101.309998,101.330002,101.309998,101.610001,101.949997,102.589996,103.040001,103.610001,103.260002,103.980003,103.180000,102.849998,102.559998,102.459999,102.239998,101.940002,101.489998,101.209999</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.104561,0.580116,0.708725,0.594154,1.107056,0.960060,0.537430,0.593620,0.551430,0.809525,1.169655,1.768974,2.181892,2.808091,2.412086,3.129470,2.357689,2.056549,1.747361,1.646583,1.405441,1.197601,0.701866,0.399284</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.103475,0.571543,0.697838,0.585604,1.086414,0.943734,0.530480,0.585828,0.544299,0.796698,1.147283,1.724315,2.117519,2.710251,2.335935,3.009685,2.285025,1.999562,1.703745,1.607050,1.374649,1.174810,0.691562,0.394511</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1.280075530736436</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>100.803040,100.856689,100.938263,100.805748,101.009712,100.765854,100.892487,100.817421,100.737198,100.922012,100.904221,100.843208,100.901993,100.916206,100.975395,100.729980,100.811867,100.926453,101.151550,100.800613,100.757828,100.803467,100.956528,100.926338</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>100.518082,100.372314,100.188591,100.154160,100.033348,99.837189,99.881798,99.830025,99.874664,99.773628,99.627068,99.670845,99.726784,99.552200,99.693390,99.733788,99.485649,99.445702,99.366356,99.404358,99.421776,99.182465,99.269409,99.103477</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:38:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>101.145905,101.088783,101.059677,101.105240,100.966934,100.949860,100.948189,100.973022,100.948837,100.991928,100.989098,101.006393,101.072350,100.986359,101.036713,101.043579,101.115723,101.043587,101.005508,101.080002,101.036125,100.941444,101.012024,101.006493</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>100.994629,100.912140,101.090286,101.080994,101.159866,101.081001,101.019188,101.007233,100.779976,101.038551,101.136299,101.212776,101.041969,101.195267,101.130089,101.004196,101.110283,101.191956,101.132149,101.083946,100.883644,100.893173,101.090485,101.063812</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>100.360451,100.302994,100.034904,99.992195,99.702522,99.534439,99.341522,99.238174,99.097061,99.086685,98.998665,98.866364,98.918449,98.821732,98.831856,98.754150,98.754990,98.656754,98.312065,98.286346,98.210670,98.202652,98.263077,98.084190</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>100.753677,100.594635,100.398445,100.415932,100.156746,99.982544,99.930214,99.901520,99.906090,99.848854,99.676430,99.684250,99.777802,99.606682,99.640549,99.697258,99.593468,99.481606,99.391235,99.463074,99.355949,99.165291,99.266289,99.183342</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>101.0064926147461</v>
+      </c>
+      <c r="G59" t="n">
+        <v>97.27999877929688</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.726493835449219</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.830688612469731</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.198991826724487</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>97.68907165527344</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>101.145905,101.088783,101.059677,101.105240,100.966934,100.949860,100.948189,100.973022,100.948837,100.991928,100.989098,101.006393,101.072350,100.986359,101.036713,101.043579,101.115723,101.043587,101.005508,101.080002,101.036125,100.941444,101.012024,101.006493</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>101.309998,100.849998,100.410004,100.620003,100.790001,100.930000,100.820000,100.959999,100.500000,98.800003,99.320000,99.040001,100.169998,98.150002,97.809998,97.360001,96.559998,97.080002,96.830002,97.029999,96.419998,97.180000,97.190002,97.279999</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.164093,0.238785,0.649673,0.485237,0.176933,0.019860,0.128189,0.013023,0.448837,2.191925,1.669098,1.966392,0.902352,2.836357,3.226715,3.683578,4.555725,3.963585,4.175506,4.050003,4.616127,3.761444,3.822022,3.726494</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.161971,0.236772,0.647021,0.482247,0.175546,0.019677,0.127147,0.012899,0.446604,2.218547,1.680526,1.985452,0.900820,2.889819,3.298963,3.783462,4.718026,4.082803,4.312203,4.173970,4.787520,3.870594,3.932525,3.830689</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.198991826724487</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>100.994629,100.912140,101.090286,101.080994,101.159866,101.081001,101.019188,101.007233,100.779976,101.038551,101.136299,101.212776,101.041969,101.195267,101.130089,101.004196,101.110283,101.191956,101.132149,101.083946,100.883644,100.893173,101.090485,101.063812</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>100.753677,100.594635,100.398445,100.415932,100.156746,99.982544,99.930214,99.901520,99.906090,99.848854,99.676430,99.684250,99.777802,99.606682,99.640549,99.697258,99.593468,99.481606,99.391235,99.463074,99.355949,99.165291,99.266289,99.183342</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>97.297134,97.317177,97.324738,97.375877,97.339996,97.380348,97.375893,97.353912,97.376022,97.366333,97.349991,97.441963,97.497345,97.438431,97.522400,97.532928,97.581650,97.558128,97.563408,97.547646,97.626686,97.642609,97.621262,97.689072</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>97.188141,97.283630,97.232567,97.441093,97.499283,97.407608,97.430817,97.266624,97.449745,97.480026,97.465759,97.791496,97.674118,97.721588,97.813591,97.495682,97.705658,97.964989,97.816818,97.668098,97.558876,97.615593,97.835831,97.769814</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>96.425819,96.397156,96.111382,96.107697,95.908096,95.736275,95.719223,95.564804,95.271439,95.141960,94.940529,94.974884,94.866837,94.716766,94.777794,94.641464,94.544853,94.452560,94.078407,93.915298,93.944069,93.988831,93.880066,93.824516</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>96.879700,96.752678,96.566544,96.523712,96.415436,96.260246,96.296638,96.164146,96.231590,96.007904,95.734741,95.879593,95.879501,95.634857,95.856857,95.823517,95.624794,95.501328,95.383400,95.399887,95.412857,95.342445,95.336571,95.325577</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>97.68907165527344</v>
+      </c>
+      <c r="G60" t="n">
+        <v>99.33999633789062</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.650924682617188</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.661893238853972</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6582423290698967</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:39</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>99.30323028564453</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>97.297134,97.317177,97.324738,97.375877,97.339996,97.380348,97.375893,97.353912,97.376022,97.366333,97.349991,97.441963,97.497345,97.438431,97.522400,97.532928,97.581650,97.558128,97.563408,97.547646,97.626686,97.642609,97.621262,97.689072</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>97.160004,97.339996,96.900002,96.970001,97.209999,97.150002,97.930000,97.500000,97.099998,96.970001,97.019997,97.150002,97.089996,97.680000,97.970001,98.610001,98.309998,97.410004,98.570000,98.620003,99.169998,99.290001,99.879997,99.339996</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.137130,0.022819,0.424736,0.405876,0.129997,0.230346,0.554107,0.146088,0.276024,0.396332,0.329994,0.291961,0.407349,0.241569,0.447601,1.077073,0.728348,0.148124,1.006592,1.072357,1.543312,1.647392,2.258735,1.650924</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.141139,0.023443,0.438325,0.418558,0.133728,0.237104,0.565820,0.149834,0.284267,0.408716,0.340130,0.300526,0.419558,0.247307,0.456876,1.092255,0.740868,0.152063,1.021195,1.087362,1.556229,1.659172,2.261449,1.661893</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6582423290698967</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>97.188141,97.283630,97.232567,97.441093,97.499283,97.407608,97.430817,97.266624,97.449745,97.480026,97.465759,97.791496,97.674118,97.721588,97.813591,97.495682,97.705658,97.964989,97.816818,97.668098,97.558876,97.615593,97.835831,97.769814</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>96.879700,96.752678,96.566544,96.523712,96.415436,96.260246,96.296638,96.164146,96.231590,96.007904,95.734741,95.879593,95.879501,95.634857,95.856857,95.823517,95.624794,95.501328,95.383400,95.399887,95.412857,95.342445,95.336571,95.325577</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:39</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>99.414062,99.510696,99.501900,99.554245,99.571472,99.570511,99.578949,99.608467,99.604912,99.517433,99.508499,99.615685,99.526657,99.446129,99.507393,99.496094,99.465996,99.442558,99.412888,99.349541,99.379555,99.303047,99.295586,99.303230</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>99.208923,99.392868,99.424286,99.445488,99.605743,99.420494,99.447418,99.548454,99.395081,99.686478,99.497932,99.716133,99.701263,99.503334,99.648895,99.450836,99.558167,99.476830,99.451172,99.392487,99.352303,99.274826,99.168900,99.336098</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>98.592506,98.671234,98.373856,98.360603,98.223694,98.073746,98.027786,98.021362,97.755356,97.564682,97.391365,97.396996,97.123634,97.036537,97.062721,96.878151,96.769058,96.697517,96.252678,95.961472,96.111786,96.076210,96.042763,95.875847</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>99.016098,98.990578,98.788269,98.759674,98.750336,98.552429,98.598335,98.633423,98.651550,98.308159,98.102234,98.164337,98.054291,97.856178,97.998619,97.990028,97.757637,97.681313,97.513573,97.444839,97.450066,97.217201,97.277084,97.164810</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>99.30323028564453</v>
+      </c>
+      <c r="G61" t="n">
+        <v>105.0400009155273</v>
+      </c>
+      <c r="H61" t="n">
+        <v>5.736770629882812</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5.461510453047593</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.659844417124998</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:56</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>104.2377090454102</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>99.414062,99.510696,99.501900,99.554245,99.571472,99.570511,99.578949,99.608467,99.604912,99.517433,99.508499,99.615685,99.526657,99.446129,99.507393,99.496094,99.465996,99.442558,99.412888,99.349541,99.379555,99.303047,99.295586,99.303230</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>99.459999,99.650002,99.940002,100.239998,100.160004,99.760002,100.019997,100.639999,100.639999,100.959999,101.199997,101.309998,101.440002,100.769997,100.900002,101.220001,101.070000,101.370003,101.540001,101.330002,102.410004,102.669998,104.480003,105.040001</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.045937,0.139306,0.438102,0.685753,0.588532,0.189491,0.441048,1.031532,1.035087,1.442566,1.691498,1.694313,1.913345,1.323868,1.392609,1.723907,1.604004,1.927445,2.127113,1.980461,3.030449,3.366951,5.184417,5.736771</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.046186,0.139795,0.438365,0.684111,0.587591,0.189947,0.440959,1.024973,1.028505,1.428849,1.671441,1.672404,1.886184,1.313752,1.380187,1.703129,1.587023,1.901396,2.094852,1.954466,2.959133,3.279391,4.962114,5.461511</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1.659844417124998</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>99.208923,99.392868,99.424286,99.445488,99.605743,99.420494,99.447418,99.548454,99.395081,99.686478,99.497932,99.716133,99.701263,99.503334,99.648895,99.450836,99.558167,99.476830,99.451172,99.392487,99.352303,99.274826,99.168900,99.336098</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>99.016098,98.990578,98.788269,98.759674,98.750336,98.552429,98.598335,98.633423,98.651550,98.308159,98.102234,98.164337,98.054291,97.856178,97.998619,97.990028,97.757637,97.681313,97.513573,97.444839,97.450066,97.217201,97.277084,97.164810</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:56</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>105.019836,105.103424,105.195190,105.312805,105.200142,105.189774,105.259537,105.150421,105.129776,105.028000,105.001991,105.046883,104.995743,104.788101,104.759567,104.685043,104.625427,104.462532,104.384224,104.364990,104.303223,104.212990,104.155540,104.237709</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>104.877106,105.121750,105.095200,105.111740,105.260956,105.204193,105.110405,105.265694,105.033112,105.314453,105.089973,105.055595,105.195328,104.906517,104.771637,104.672974,104.693535,104.555473,104.457901,104.469116,104.004791,104.364128,104.275871,104.155876</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>103.457237,103.314423,103.168213,103.116066,102.844131,102.580948,102.584290,102.329391,102.197815,101.976494,101.859505,101.801636,101.728394,101.440765,101.359497,101.146233,100.999352,100.838272,100.425766,100.179550,100.361153,100.119637,100.121765,100.053360</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>104.130280,104.012619,103.918098,103.896858,103.609497,103.363480,103.492119,103.250130,103.299713,102.952072,102.745560,102.817116,102.836433,102.389565,102.452827,102.403694,102.249382,101.996048,101.749771,101.756317,101.694572,101.371033,101.428642,101.380684</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>104.2377090454102</v>
+      </c>
+      <c r="G62" t="n">
+        <v>113.1900024414062</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8.952293395996051</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7.909084904057918</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.867637285628824</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:48</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>112.4688568115234</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>105.019836,105.103424,105.195190,105.312805,105.200142,105.189774,105.259537,105.150421,105.129776,105.028000,105.001991,105.046883,104.995743,104.788101,104.759567,104.685043,104.625427,104.462532,104.384224,104.364990,104.303223,104.212990,104.155540,104.237709</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>105.279999,105.480003,105.690002,106.279999,106.330002,106.190002,105.639999,105.690002,108.470001,110.709999,111.129997,111.660004,112.570000,112.129997,114.330002,113.510002,113.169998,113.110001,112.699997,113.629997,113.389999,113.580002,113.209999,113.190002</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.260163,0.376579,0.494812,0.967194,1.129860,1.000228,0.380462,0.539581,3.340225,5.681999,6.128006,6.613121,7.574257,7.341896,9.570435,8.824959,8.544571,8.647469,8.315773,9.265007,9.086776,9.367012,9.054459,8.952293</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.247115,0.357015,0.468173,0.910043,1.062597,0.941923,0.360150,0.510532,3.079400,5.132327,5.514268,5.922551,6.728486,6.547665,8.370887,7.774609,7.550209,7.645185,7.378681,8.153663,8.013737,8.247061,7.997932,7.909085</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>4.867637285628824</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>104.877106,105.121750,105.095200,105.111740,105.260956,105.204193,105.110405,105.265694,105.033112,105.314453,105.089973,105.055595,105.195328,104.906517,104.771637,104.672974,104.693535,104.555473,104.457901,104.469116,104.004791,104.364128,104.275871,104.155876</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>104.130280,104.012619,103.918098,103.896858,103.609497,103.363480,103.492119,103.250130,103.299713,102.952072,102.745560,102.817116,102.836433,102.389565,102.452827,102.403694,102.249382,101.996048,101.749771,101.756317,101.694572,101.371033,101.428642,101.380684</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:48</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>113.232727,113.096939,113.228760,113.246330,113.210381,113.274017,113.209152,113.126366,113.227615,113.111008,113.194633,113.111084,113.091042,112.897049,112.974792,112.826385,112.953140,112.875160,112.775604,112.775017,112.684731,112.530693,112.521484,112.468857</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>113.032715,112.807922,113.136230,113.049759,112.984123,113.196281,112.753326,113.035965,112.725250,112.867271,112.964233,112.677795,112.477692,112.601646,112.634140,112.367752,112.488113,112.165665,112.064278,112.341026,112.104630,112.216919,112.010010,111.745956</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>111.876320,111.558098,111.308197,111.081879,110.853409,110.586403,110.198425,109.933624,109.811584,109.508102,109.328102,109.004921,108.970940,108.517914,108.366608,108.089699,107.945847,107.779854,107.052467,106.694092,106.566002,106.402321,106.173279,106.094460</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>112.539932,112.172394,112.021187,112.041870,111.817200,111.533997,111.488190,111.219215,111.360138,111.047112,110.929337,110.764069,110.662643,110.259689,110.264458,110.241859,110.103310,109.861847,109.377037,109.307442,109.076149,108.636894,108.617340,108.516876</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>112.4688568115234</v>
+      </c>
+      <c r="G63" t="n">
+        <v>109.0999984741211</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.368858337402301</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.087862863904078</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.767759020010986</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:53</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>107.9907073974609</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>113.232727,113.096939,113.228760,113.246330,113.210381,113.274017,113.209152,113.126366,113.227615,113.111008,113.194633,113.111084,113.091042,112.897049,112.974792,112.826385,112.953140,112.875160,112.775604,112.775017,112.684731,112.530693,112.521484,112.468857</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>111.900002,111.790001,111.559998,112.199997,111.790001,111.580002,111.849998,111.730003,111.580002,111.750000,111.589996,111.959999,111.370003,111.120003,111.139999,111.070000,110.500000,110.620003,111.019997,110.930000,110.120003,107.620003,108.860001,109.099998</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.332725,1.306938,1.668762,1.046333,1.420380,1.694015,1.359154,1.396363,1.647613,1.361008,1.604637,1.151085,1.721039,1.777046,1.834793,1.756385,2.453140,2.255157,1.755607,1.845017,2.564728,4.910690,3.661483,3.368859</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1.190997,1.169101,1.495843,0.932561,1.270579,1.518207,1.215157,1.249765,1.476620,1.217904,1.437975,1.028122,1.545335,1.599214,1.650884,1.581332,2.220036,2.038652,1.581343,1.663226,2.329030,4.562990,3.363479,3.087863</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1.767759020010986</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>113.032715,112.807922,113.136230,113.049759,112.984123,113.196281,112.753326,113.035965,112.725250,112.867271,112.964233,112.677795,112.477692,112.601646,112.634140,112.367752,112.488113,112.165665,112.064278,112.341026,112.104630,112.216919,112.010010,111.745956</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>112.539932,112.172394,112.021187,112.041870,111.817200,111.533997,111.488190,111.219215,111.360138,111.047112,110.929337,110.764069,110.662643,110.259689,110.264458,110.241859,110.103310,109.861847,109.377037,109.307442,109.076149,108.636894,108.617340,108.516876</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:53</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>109.099800,109.004112,108.988449,108.904167,108.825912,108.825691,108.817635,108.697784,108.675697,108.533951,108.577423,108.551888,108.514359,108.424217,108.540756,108.403671,108.419136,108.408516,108.250053,108.285950,108.259514,108.173798,108.091095,107.990707</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>108.906242,108.944588,108.860878,108.803093,108.923874,108.952057,108.576874,108.670746,108.485466,108.531647,108.528580,108.513062,108.292473,108.523842,108.473442,108.120285,108.252274,108.026794,108.100418,108.076996,108.035156,107.887375,108.030945,107.910271</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>107.934776,107.692657,107.424667,107.243454,107.025208,106.792961,106.641678,106.398544,105.950928,105.706902,105.511780,105.512306,105.387344,105.032616,104.971893,104.685287,104.445007,104.435898,103.800598,103.649734,103.561577,103.374649,103.211426,103.070221</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>108.519661,108.175278,108.032867,107.897583,107.768341,107.573029,107.507835,107.262306,107.236763,106.923218,106.811760,106.819214,106.675484,106.334076,106.441589,106.263542,106.088089,106.017593,105.626862,105.674934,105.500854,105.256119,105.119041,105.013863</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>107.9907073974609</v>
+      </c>
+      <c r="G64" t="n">
+        <v>111.4000015258789</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.409294128418011</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.060407613752152</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.3867179940408</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:46</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>110.7206268310547</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>109.099800,109.004112,108.988449,108.904167,108.825912,108.825691,108.817635,108.697784,108.675697,108.533951,108.577423,108.551888,108.514359,108.424217,108.540756,108.403671,108.419136,108.408516,108.250053,108.285950,108.259514,108.173798,108.091095,107.990707</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>108.720001,108.410004,108.430000,108.029999,108.250000,107.980003,108.410004,108.349998,108.199997,108.110001,108.779999,110.309998,109.889999,109.370003,110.419998,110.099998,109.860001,111.019997,111.139999,112.279999,110.930000,111.190002,111.519997,111.400002</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.379799,0.594108,0.558449,0.874168,0.575912,0.845688,0.407631,0.347786,0.475700,0.423950,0.202576,1.758110,1.375640,0.945786,1.879242,1.696327,1.440865,2.611481,2.889946,3.994049,2.670486,3.016204,3.428902,3.409295</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.349337,0.548020,0.515032,0.809190,0.532020,0.783189,0.376009,0.320983,0.439649,0.392147,0.186225,1.593790,1.251834,0.864758,1.701904,1.540715,1.311546,2.352262,2.600276,3.557222,2.407362,2.712658,3.074697,3.060408</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.3867179940408</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>108.906242,108.944588,108.860878,108.803093,108.923874,108.952057,108.576874,108.670746,108.485466,108.531647,108.528580,108.513062,108.292473,108.523842,108.473442,108.120285,108.252274,108.026794,108.100418,108.076996,108.035156,107.887375,108.030945,107.910271</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>108.519661,108.175278,108.032867,107.897583,107.768341,107.573029,107.507835,107.262306,107.236763,106.923218,106.811760,106.819214,106.675484,106.334076,106.441589,106.263542,106.088089,106.017593,105.626862,105.674934,105.500854,105.256119,105.119041,105.013863</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:46</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>111.240875,111.248833,111.306946,111.337036,111.338806,111.407944,111.252998,111.234482,111.257584,111.120667,111.103874,111.113220,111.100281,110.958725,111.004639,110.938629,111.008217,110.945107,110.868217,110.836914,110.927826,110.812363,110.813774,110.720627</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>111.031586,111.004501,111.329208,111.494751,111.345413,111.475258,110.957428,111.517639,110.894829,111.378540,111.188492,110.998108,110.890137,111.028542,110.914803,110.819519,110.841599,110.652908,110.744133,110.763786,110.781898,110.923264,110.733307,110.560555</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>110.032188,109.945747,109.893951,109.921074,109.744766,109.531754,109.366295,109.253830,108.916489,108.703339,108.531731,108.452896,108.355980,108.019348,107.924255,107.827744,107.768387,107.722336,107.212997,106.837570,106.993317,106.821411,106.666023,106.493286</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>110.562950,110.479454,110.508095,110.469658,110.378700,110.217323,110.105286,110.010193,109.934982,109.732063,109.558029,109.554344,109.493080,109.105072,109.141541,109.117851,109.026466,108.971710,108.639969,108.569305,108.565628,108.319023,108.201263,108.148323</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>110.7206268310547</v>
+      </c>
+      <c r="G65" t="n">
+        <v>116.5999984741211</v>
+      </c>
+      <c r="H65" t="n">
+        <v>5.879371643066392</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5.042342813041541</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.90345373272727</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:44</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>115.2191619873047</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>111.240875,111.248833,111.306946,111.337036,111.338806,111.407944,111.252998,111.234482,111.257584,111.120667,111.103874,111.113220,111.100281,110.958725,111.004639,110.938629,111.008217,110.945107,110.868217,110.836914,110.927826,110.812363,110.813774,110.720627</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>111.739998,112.169998,112.080002,115.320000,115.940002,115.980003,116.769997,116.790001,118.010002,118.040001,117.919998,117.529999,117.190002,117.730003,118.339996,119.209999,119.110001,119.419998,118.900002,118.320000,117.559998,116.889999,116.779999,116.599998</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.499123,0.921165,0.773056,3.982964,4.601196,4.572059,5.516999,5.555519,6.752418,6.919334,6.816124,6.416779,6.089721,6.771278,7.335357,8.271370,8.101784,8.474891,8.031785,7.483086,6.632172,6.077636,5.966225,5.879371</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.446682,0.821222,0.689736,3.453836,3.968601,3.942110,4.724671,4.756845,5.721903,5.861855,5.780295,5.459694,5.196451,5.751532,6.198545,6.938487,6.801934,7.096710,6.755075,6.324447,5.641521,5.199449,5.108944,5.042343</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4.90345373272727</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>111.031586,111.004501,111.329208,111.494751,111.345413,111.475258,110.957428,111.517639,110.894829,111.378540,111.188492,110.998108,110.890137,111.028542,110.914803,110.819519,110.841599,110.652908,110.744133,110.763786,110.781898,110.923264,110.733307,110.560555</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>110.562950,110.479454,110.508095,110.469658,110.378700,110.217323,110.105286,110.010193,109.934982,109.732063,109.558029,109.554344,109.493080,109.105072,109.141541,109.117851,109.026466,108.971710,108.639969,108.569305,108.565628,108.319023,108.201263,108.148323</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:44</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>116.461044,116.215553,116.217438,116.234268,116.043930,115.997505,115.971939,115.849510,115.898285,115.733658,115.711845,115.740562,115.531746,115.402573,115.516678,115.389992,115.542168,115.535477,115.505211,115.321274,115.469482,115.321899,115.244781,115.219162</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>116.171043,115.867966,116.071014,116.286713,115.908585,115.890366,115.380798,115.911133,115.386398,115.929314,115.671524,115.507751,115.010574,115.328857,115.159874,115.262283,115.447906,115.219414,115.197906,115.191696,115.194687,115.280632,115.059738,114.874229</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>115.084480,114.735657,114.481766,114.338669,114.118607,113.813644,113.608047,113.261192,113.002243,112.683205,112.566231,112.456779,112.287033,111.939629,111.734215,111.611229,111.595856,111.630257,111.142944,110.509018,110.693390,110.476379,110.321815,110.278305</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>115.669212,115.313507,115.172516,115.129776,114.883728,114.588089,114.612411,114.249252,114.236031,113.970779,113.873680,113.908691,113.649109,113.237305,113.205063,113.142876,113.090988,113.031639,112.843391,112.535278,112.518784,112.201172,112.113976,112.058327</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>115.2191619873047</v>
+      </c>
+      <c r="G66" t="n">
+        <v>119.4400024414062</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4.220840454101548</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3.53385831197732</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.777097929756138</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:08</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>119.939811706543</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>116.461044,116.215553,116.217438,116.234268,116.043930,115.997505,115.971939,115.849510,115.898285,115.733658,115.711845,115.740562,115.531746,115.402573,115.516678,115.389992,115.542168,115.535477,115.505211,115.321274,115.469482,115.321899,115.244781,115.219162</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>116.809998,116.510002,116.290001,117.489998,117.440002,116.839996,117.309998,117.419998,117.940002,116.900002,117.370003,117.459999,117.980003,118.160004,118.220001,118.019997,118.099998,118.470001,118.559998,118.809998,118.339996,118.489998,119.129997,119.440002</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.348954,0.294449,0.072563,1.255730,1.396072,0.842491,1.338059,1.570488,2.041717,1.166344,1.658158,1.719437,2.448257,2.757431,2.703323,2.630005,2.557830,2.934524,3.054787,3.488724,2.870514,3.168099,3.885216,4.220840</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.298736,0.252724,0.062398,1.068797,1.188754,0.721064,1.140618,1.337496,1.731149,0.997728,1.412761,1.463849,2.075146,2.333641,2.286689,2.228440,2.165818,2.477019,2.576574,2.936389,2.425650,2.673727,3.261325,3.533858</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.777097929756138</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>116.171043,115.867966,116.071014,116.286713,115.908585,115.890366,115.380798,115.911133,115.386398,115.929314,115.671524,115.507751,115.010574,115.328857,115.159874,115.262283,115.447906,115.219414,115.197906,115.191696,115.194687,115.280632,115.059738,114.874229</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>115.669212,115.313507,115.172516,115.129776,114.883728,114.588089,114.612411,114.249252,114.236031,113.970779,113.873680,113.908691,113.649109,113.237305,113.205063,113.142876,113.090988,113.031639,112.843391,112.535278,112.518784,112.201172,112.113976,112.058327</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:08</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>119.449768,119.463837,119.692963,119.861732,119.806526,119.933403,119.895264,119.906754,120.049316,119.888336,119.916214,119.995674,119.851418,119.794579,119.890564,119.894318,120.114281,119.969223,119.970726,119.923874,120.051888,119.892097,119.901993,119.939812</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>118.910736,119.137535,119.696991,119.868683,119.729187,119.557686,119.351753,119.893311,119.277267,119.881416,119.742149,119.666763,119.375168,119.543137,119.566940,119.874733,119.808777,119.465645,119.623795,119.696808,119.694336,120.014610,119.499603,119.466736</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>118.312752,118.172729,118.108704,118.169693,118.232025,117.992035,117.853378,117.867302,117.653389,117.301979,117.249107,117.220444,117.142578,116.719749,116.598175,116.603485,116.616974,116.617020,116.159592,115.569656,115.788452,115.559464,115.403885,115.454895</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>118.812340,118.687759,118.876129,118.958427,118.850471,118.685753,118.793930,118.648727,118.689407,118.343185,118.357040,118.446396,118.331741,117.878036,117.863487,118.024010,118.013847,117.941788,117.667877,117.416359,117.427582,117.108543,117.066452,117.120491</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>119.939811706543</v>
+      </c>
+      <c r="G67" t="n">
+        <v>114.7699966430664</v>
+      </c>
+      <c r="H67" t="n">
+        <v>5.169815063476591</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.504500492018543</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.567401527716628</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:21</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>114.3383636474609</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>119.449768,119.463837,119.692963,119.861732,119.806526,119.933403,119.895264,119.906754,120.049316,119.888336,119.916214,119.995674,119.851418,119.794579,119.890564,119.894318,120.114281,119.969223,119.970726,119.923874,120.051888,119.892097,119.901993,119.939812</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>118.379997,118.949997,117.900002,117.389999,117.379997,117.620003,117.080002,116.889999,116.779999,115.150002,113.870003,114.400002,114.540001,114.279999,114.510002,114.029999,114.699997,115.129997,114.900002,115.129997,114.699997,115.279999,114.690002,114.769997</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.069771,0.513840,1.792961,2.471733,2.426529,2.313400,2.815262,3.016755,3.269317,4.738334,6.046211,5.595672,5.311417,5.514580,5.380562,5.864319,5.414284,4.839226,5.070724,4.793877,5.351891,4.612098,5.211991,5.169815</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.903675,0.431980,1.520748,2.105573,2.067242,1.966843,2.404563,2.580849,2.799552,4.114924,5.309749,4.891322,4.637172,4.825499,4.698770,5.142786,4.720387,4.203271,4.413163,4.163882,4.665991,4.000779,4.544416,4.504501</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.567401527716628</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>118.910736,119.137535,119.696991,119.868683,119.729187,119.557686,119.351753,119.893311,119.277267,119.881416,119.742149,119.666763,119.375168,119.543137,119.566940,119.874733,119.808777,119.465645,119.623795,119.696808,119.694336,120.014610,119.499603,119.466736</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>118.812340,118.687759,118.876129,118.958427,118.850471,118.685753,118.793930,118.648727,118.689407,118.343185,118.357040,118.446396,118.331741,117.878036,117.863487,118.024010,118.013847,117.941788,117.667877,117.416359,117.427582,117.108543,117.066452,117.120491</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:21</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>114.669968,114.595200,114.661179,114.655174,114.566315,114.586037,114.583572,114.581741,114.581390,114.468842,114.494400,114.581596,114.543037,114.410637,114.507233,114.416718,114.555313,114.488045,114.466286,114.420898,114.427757,114.374847,114.346901,114.338364</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>114.205048,114.397171,114.708336,114.668198,114.654358,114.585724,114.320724,114.462204,114.422318,114.598091,114.379601,114.432037,114.221786,114.357819,114.465034,114.465836,114.292389,114.341255,114.579536,114.261749,114.199310,114.543655,114.248016,114.037239</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>113.554672,113.361084,113.229202,113.149376,112.997116,112.713058,112.629333,112.636658,112.270309,112.030075,111.903114,111.908203,111.849358,111.464401,111.333107,111.256516,111.076233,111.048279,110.563286,110.169456,110.240837,110.117928,109.866890,109.745674</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>114.047333,113.869316,113.836845,113.743355,113.495880,113.340691,113.366791,113.298599,113.262718,112.980263,112.811203,112.939766,112.947655,112.476791,112.548973,112.548004,112.403397,112.273239,112.020950,111.930077,111.832825,111.595261,111.528320,111.423111</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>114.3383636474609</v>
+      </c>
+      <c r="G68" t="n">
+        <v>116.9599990844727</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.621635437011761</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.241480384347749</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.5080331067578</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:39</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>116.6824493408203</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>114.669968,114.595200,114.661179,114.655174,114.566315,114.586037,114.583572,114.581741,114.581390,114.468842,114.494400,114.581596,114.543037,114.410637,114.507233,114.416718,114.555313,114.488045,114.466286,114.420898,114.427757,114.374847,114.346901,114.338364</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>114.820000,114.809998,115.510002,114.110001,113.099998,113.349998,113.330002,113.790001,114.949997,114.589996,116.260002,117.059998,116.739998,117.370003,117.290001,116.820000,116.839996,116.580002,117.019997,117.400002,117.459999,116.879997,116.849998,116.959999</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.150032,0.214798,0.848823,0.545173,1.466317,1.236039,1.253570,0.791740,0.368607,0.121154,1.765602,2.478402,2.196961,2.959366,2.782768,2.403282,2.284683,2.091957,2.553711,2.979104,3.032242,2.505150,2.503097,2.621635</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.130667,0.187090,0.734848,0.477761,1.296478,1.090462,1.106124,0.695791,0.320667,0.105729,1.518667,2.117206,1.881926,2.521399,2.372553,2.057252,1.955395,1.794439,2.182286,2.537567,2.581510,2.143352,2.142146,2.241480</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1.5080331067578</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>114.205048,114.397171,114.708336,114.668198,114.654358,114.585724,114.320724,114.462204,114.422318,114.598091,114.379601,114.432037,114.221786,114.357819,114.465034,114.465836,114.292389,114.341255,114.579536,114.261749,114.199310,114.543655,114.248016,114.037239</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>114.047333,113.869316,113.836845,113.743355,113.495880,113.340691,113.366791,113.298599,113.262718,112.980263,112.811203,112.939766,112.947655,112.476791,112.548973,112.548004,112.403397,112.273239,112.020950,111.930077,111.832825,111.595261,111.528320,111.423111</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:39</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>116.783821,116.736900,116.816498,116.899254,116.781395,116.764969,116.840065,116.869736,116.876801,116.810677,116.842072,116.991753,116.860069,116.769798,116.879990,116.777367,116.889267,116.804909,116.768265,116.659409,116.715469,116.783020,116.681931,116.682449</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>116.441078,116.551720,116.740784,116.775406,116.837486,116.662933,116.583817,116.817924,116.598862,116.845337,116.787285,116.656792,116.590492,116.635666,116.673241,116.466324,116.645729,116.505890,116.601059,116.442802,116.470985,116.720421,116.543076,116.346794</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>115.629745,115.526413,115.386353,115.376610,115.259949,114.969818,114.933739,114.889740,114.640930,114.425079,114.410446,114.326942,114.196579,113.882523,113.806152,113.682976,113.490685,113.508499,113.068314,112.599594,112.753983,112.699539,112.466537,112.422966</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>116.114365,116.012543,115.957237,115.999664,115.832214,115.591621,115.751221,115.653130,115.568840,115.361679,115.276123,115.414101,115.295357,114.841423,114.954971,114.891373,114.700188,114.675400,114.401939,114.197533,114.162994,114.146271,114.040527,113.958549</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>116.6824493408203</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120.5400009155273</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.857551574707045</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.20022527410661</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.875068494206963</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:29</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>120.2732543945312</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>116.783821,116.736900,116.816498,116.899254,116.781395,116.764969,116.840065,116.869736,116.876801,116.810677,116.842072,116.991753,116.860069,116.769798,116.879990,116.777367,116.889267,116.804909,116.768265,116.659409,116.715469,116.783020,116.681931,116.682449</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>116.400002,116.250000,116.360001,117.290001,118.379997,119.160004,120.809998,120.699997,119.480003,120.419998,120.080002,120.849998,121.000000,121.919998,121.849998,121.559998,120.989998,122.180000,122.150002,121.529999,122.029999,121.589996,120.629997,120.540001</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.383819,0.486900,0.456497,0.390747,1.598602,2.395035,3.969933,3.830261,2.603202,3.609321,3.237930,3.858245,4.139931,5.150200,4.970008,4.782631,4.100731,5.375091,5.381737,4.870590,5.314530,4.806976,3.948066,3.857552</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.329742,0.418839,0.392315,0.333146,1.350399,2.009932,3.286096,3.173373,2.178777,2.997277,2.696477,3.192590,3.421431,4.224246,4.078792,3.934379,3.389314,4.399322,4.405842,4.007726,4.355101,3.953431,3.272873,3.200226</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2.875068494206963</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>116.441078,116.551720,116.740784,116.775406,116.837486,116.662933,116.583817,116.817924,116.598862,116.845337,116.787285,116.656792,116.590492,116.635666,116.673241,116.466324,116.645729,116.505890,116.601059,116.442802,116.470985,116.720421,116.543076,116.346794</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>116.114365,116.012543,115.957237,115.999664,115.832214,115.591621,115.751221,115.653130,115.568840,115.361679,115.276123,115.414101,115.295357,114.841423,114.954971,114.891373,114.700188,114.675400,114.401939,114.197533,114.162994,114.146271,114.040527,113.958549</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:29</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>120.424454,120.372025,120.407379,120.424507,120.299652,120.342796,120.431213,120.366402,120.411522,120.379623,120.384918,120.518234,120.284805,120.244026,120.372238,120.303291,120.456261,120.407669,120.388405,120.313820,120.319031,120.351410,120.302132,120.273254</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>120.020195,120.141663,120.267532,120.303680,120.304077,120.117706,120.028160,120.170258,120.027573,120.415680,120.315056,120.174255,119.849098,120.026245,120.026527,120.079277,120.201553,120.083298,120.016853,119.980972,119.972488,120.213020,119.969498,119.792610</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>119.055969,118.923012,118.607086,118.416107,118.268173,118.031616,118.068153,117.920563,117.788414,117.591934,117.455154,117.383530,117.327415,117.033173,117.013924,116.970108,116.800034,116.771019,116.446579,116.022293,116.016510,115.999603,115.864044,115.909805</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>119.590698,119.435844,119.316460,119.258621,119.011726,118.876602,119.107628,118.844742,118.906700,118.638306,118.499924,118.623772,118.462440,118.086349,118.210869,118.204643,118.159958,117.953690,117.812767,117.541992,117.451271,117.362381,117.403198,117.287735</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>120.2732543945312</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120.1399993896484</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1332550048827557</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1109164354584117</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.5009297528780955</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:27</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>119.9238586425781</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>120.424454,120.372025,120.407379,120.424507,120.299652,120.342796,120.431213,120.366402,120.411522,120.379623,120.384918,120.518234,120.284805,120.244026,120.372238,120.303291,120.456261,120.407669,120.388405,120.313820,120.319031,120.351410,120.302132,120.273254</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>120.510002,120.209999,120.750000,120.680000,119.959999,120.620003,121.260002,121.059998,120.760002,120.949997,121.860001,121.620003,121.480003,121.040001,121.120003,120.339996,121.300003,121.120003,121.379997,120.800003,121.410004,121.129997,120.580002,120.139999</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.085548,0.162026,0.342621,0.255493,0.339653,0.277207,0.828789,0.693596,0.348480,0.570374,1.475083,1.101769,1.195198,0.795975,0.747765,0.036705,0.843742,0.712334,0.991592,0.486183,1.090973,0.778587,0.277870,0.133255</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.070988,0.134786,0.283744,0.211711,0.283138,0.229818,0.683481,0.572935,0.288572,0.471578,1.210473,0.905911,0.983864,0.657613,0.617375,0.030501,0.695583,0.588122,0.816932,0.402469,0.898585,0.642770,0.230444,0.110916</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.5009297528780955</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>120.020195,120.141663,120.267532,120.303680,120.304077,120.117706,120.028160,120.170258,120.027573,120.415680,120.315056,120.174255,119.849098,120.026245,120.026527,120.079277,120.201553,120.083298,120.016853,119.980972,119.972488,120.213020,119.969498,119.792610</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>119.590698,119.435844,119.316460,119.258621,119.011726,118.876602,119.107628,118.844742,118.906700,118.638306,118.499924,118.623772,118.462440,118.086349,118.210869,118.204643,118.159958,117.953690,117.812767,117.541992,117.451271,117.362381,117.403198,117.287735</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:27</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>120.149109,120.026306,119.998505,120.050888,119.954109,120.067703,120.057938,119.978516,120.062576,120.035774,119.987999,120.090866,119.934784,119.898178,119.967064,119.878555,120.081070,120.020012,119.955032,120.050514,120.106598,119.984016,119.960175,119.923859</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>119.831055,119.869980,119.929573,119.834518,120.221718,120.038673,119.616997,119.892838,119.690178,119.976578,119.992538,119.686798,119.595741,119.759743,119.770874,119.834969,119.745316,119.650330,119.605980,119.655807,119.711052,119.893822,119.769440,119.505920</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>119.148750,118.979935,118.713791,118.619095,118.546829,118.434814,118.385681,118.303642,118.125290,117.917244,117.704437,117.596100,117.445419,117.101433,116.992203,116.790924,116.744003,116.729805,116.237915,115.929337,115.978821,115.775810,115.620422,115.623627</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>119.572540,119.375084,119.283623,119.250717,119.124748,119.028587,119.120354,118.966324,119.006523,118.730293,118.545410,118.688705,118.512573,118.069382,118.114502,118.056686,118.140182,117.969131,117.702988,117.539902,117.505463,117.286034,117.225983,117.161316</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>119.9238586425781</v>
+      </c>
+      <c r="G71" t="n">
+        <v>119.7699966430664</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1538619995116903</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1284645602606331</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.801220266739251</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>119.9646377563477</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>120.149109,120.026306,119.998505,120.050888,119.954109,120.067703,120.057938,119.978516,120.062576,120.035774,119.987999,120.090866,119.934784,119.898178,119.967064,119.878555,120.081070,120.020012,119.955032,120.050514,120.106598,119.984016,119.960175,119.923859</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>121.309998,123.980003,124.089996,124.440002,124.000000,123.900002,123.320000,123.139999,121.690002,121.750000,121.809998,122.050003,123.279999,123.019997,122.690002,122.830002,121.370003,121.980003,121.660004,120.709999,120.000000,119.820000,119.959999,119.769997</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1.160889,3.953697,4.091491,4.389114,4.045891,3.832299,3.262062,3.161483,1.627426,1.714226,1.821999,1.959137,3.345215,3.121819,2.722938,2.951447,1.288933,1.959991,1.704972,0.659485,0.106598,0.164016,0.000176,0.153862</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.956960,3.188980,3.297197,3.527093,3.262815,3.093058,2.645201,2.567389,1.337354,1.407989,1.495771,1.605192,2.713510,2.537651,2.219365,2.402871,1.061986,1.606814,1.401423,0.546338,0.088832,0.136886,0.000147,0.128465</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1.801220266739251</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>119.831055,119.869980,119.929573,119.834518,120.221718,120.038673,119.616997,119.892838,119.690178,119.976578,119.992538,119.686798,119.595741,119.759743,119.770874,119.834969,119.745316,119.650330,119.605980,119.655807,119.711052,119.893822,119.769440,119.505920</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>119.572540,119.375084,119.283623,119.250717,119.124748,119.028587,119.120354,118.966324,119.006523,118.730293,118.545410,118.688705,118.512573,118.069382,118.114502,118.056686,118.140182,117.969131,117.702988,117.539902,117.505463,117.286034,117.225983,117.161316</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>119.726349,119.652466,119.593338,119.616684,119.519333,119.570114,119.658913,119.535385,119.537315,119.516563,119.507942,119.584335,119.530182,119.565865,119.676361,119.652969,119.855171,119.848572,119.861534,119.909477,119.879898,119.907471,119.970528,119.964638</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>119.313858,119.701889,119.637749,119.441582,119.666847,119.661377,119.516968,119.350479,119.326477,119.511398,119.527618,119.563065,119.235817,119.531891,119.551956,119.772125,119.646843,119.628944,119.705681,119.538437,119.727539,119.664642,119.908890,119.678482</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>118.421173,118.189064,117.924713,117.838493,117.710014,117.619446,117.667732,117.496620,117.305611,117.017830,116.922493,116.801506,116.781670,116.508881,116.428070,116.293549,116.354645,116.342316,115.840843,115.560600,115.589020,115.424934,115.428551,115.377327</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>118.930664,118.725990,118.591919,118.494118,118.339050,118.251556,118.422569,118.204910,118.221825,117.842812,117.664856,117.881195,117.841614,117.479446,117.558189,117.532333,117.648178,117.416634,117.260223,117.136597,117.022614,116.949982,117.021523,116.852615</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>119.9646377563477</v>
+      </c>
+      <c r="G72" t="n">
+        <v>118.0699996948242</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.89463806152348</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.604673555027149</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.129467663745357</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:57</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>118.4377212524414</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>119.726349,119.652466,119.593338,119.616684,119.519333,119.570114,119.658913,119.535385,119.537315,119.516563,119.507942,119.584335,119.530182,119.565865,119.676361,119.652969,119.855171,119.848572,119.861534,119.909477,119.879898,119.907471,119.970528,119.964638</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>118.690002,117.989998,118.300003,117.720001,118.430000,118.690002,119.989998,119.809998,118.000000,118.709999,119.260002,119.699997,119.949997,118.320000,118.779999,117.680000,118.540001,118.820000,118.070000,117.059998,116.900002,117.809998,117.650002,118.070000</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.036347,1.662468,1.293335,1.896683,1.089333,0.880112,0.331085,0.274613,1.537315,0.806564,0.247940,0.115662,0.419815,1.245865,0.896362,1.972969,1.315170,1.028572,1.791534,2.849479,2.979896,2.097473,2.320526,1.894638</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.873154,1.408991,1.093267,1.611181,0.919811,0.741521,0.275927,0.229207,1.302809,0.679441,0.207899,0.096627,0.349992,1.052963,0.754641,1.676554,1.109474,0.865656,1.517349,2.434204,2.549099,1.780387,1.972398,1.604674</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1.129467663745357</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>119.313858,119.701889,119.637749,119.441582,119.666847,119.661377,119.516968,119.350479,119.326477,119.511398,119.527618,119.563065,119.235817,119.531891,119.551956,119.772125,119.646843,119.628944,119.705681,119.538437,119.727539,119.664642,119.908890,119.678482</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>118.930664,118.725990,118.591919,118.494118,118.339050,118.251556,118.422569,118.204910,118.221825,117.842812,117.664856,117.881195,117.841614,117.479446,117.558189,117.532333,117.648178,117.416634,117.260223,117.136597,117.022614,116.949982,117.021523,116.852615</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:57</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>117.997826,117.965294,118.000015,118.132370,118.098557,118.251663,118.346512,118.292526,118.344887,118.369881,118.305374,118.420395,118.420441,118.395889,118.421722,118.429115,118.497772,118.392838,118.417168,118.449318,118.487907,118.397293,118.394753,118.437721</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>117.803421,118.046783,117.944641,118.123848,118.275658,118.432350,118.340614,118.378510,118.153259,118.361534,118.282669,118.375031,118.340721,118.582184,118.416428,118.413322,118.213638,118.289703,118.609932,117.900215,118.241280,118.122047,118.308289,118.179558</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>116.852875,116.608017,116.377983,116.385513,116.253838,116.191376,116.233444,115.983986,115.924698,115.641228,115.523621,115.430397,115.403877,115.049088,115.049026,114.935822,114.859779,114.754921,114.250549,113.904869,114.010498,113.729507,113.607430,113.647041</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>117.283508,117.120529,116.972374,117.013641,116.866158,116.879204,117.040367,116.838028,116.852112,116.604393,116.377495,116.654068,116.584549,116.155769,116.257957,116.260757,116.142235,115.890533,115.726143,115.584305,115.525108,115.291031,115.339966,115.286667</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>118.4377212524414</v>
+      </c>
+      <c r="G73" t="n">
+        <v>118.4400024414062</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00228118896484375</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.00192602914371965</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8390038283983128</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:33</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>118.5425415039062</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>117.997826,117.965294,118.000015,118.132370,118.098557,118.251663,118.346512,118.292526,118.344887,118.369881,118.305374,118.420395,118.420441,118.395889,118.421722,118.429115,118.497772,118.392838,118.417168,118.449318,118.487907,118.397293,118.394753,118.437721</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>119.199997,119.489998,119.139999,119.879997,119.389999,120.120003,120.860001,120.949997,120.190002,118.190002,118.019997,117.699997,119.120003,118.779999,119.019997,118.919998,119.089996,119.080002,118.910004,119.410004,119.650002,119.110001,118.739998,118.440002</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.202171,1.524704,1.139984,1.747627,1.291442,1.868340,2.513489,2.657471,1.845115,0.179879,0.285377,0.720398,0.699562,0.384110,0.598275,0.490883,0.592224,0.687164,0.492836,0.960686,1.162095,0.712708,0.345245,0.002281</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.008533,1.276010,0.956844,1.457814,1.081701,1.555394,2.079670,2.197165,1.535165,0.152194,0.241804,0.612063,0.587275,0.323379,0.502667,0.412784,0.497291,0.577061,0.414461,0.804527,0.971245,0.598361,0.290757,0.001926</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8390038283983128</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>117.803421,118.046783,117.944641,118.123848,118.275658,118.432350,118.340614,118.378510,118.153259,118.361534,118.282669,118.375031,118.340721,118.582184,118.416428,118.413322,118.213638,118.289703,118.609932,117.900215,118.241280,118.122047,118.308289,118.179558</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>117.283508,117.120529,116.972374,117.013641,116.866158,116.879204,117.040367,116.838028,116.852112,116.604393,116.377495,116.654068,116.584549,116.155769,116.257957,116.260757,116.142235,115.890533,115.726143,115.584305,115.525108,115.291031,115.339966,115.286667</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:33</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>118.402260,118.368950,118.425438,118.482544,118.428398,118.450348,118.574562,118.514725,118.467888,118.465584,118.408791,118.552086,118.557625,118.535088,118.666679,118.651779,118.794456,118.707451,118.668823,118.694878,118.674507,118.639069,118.531509,118.542542</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>118.132370,118.465988,118.315414,118.274063,118.508316,118.434975,118.526360,118.280815,118.372528,118.620651,118.374275,118.350983,118.344482,118.546280,118.710182,118.512497,118.643143,118.566086,118.696579,118.250603,118.454399,118.373131,118.520584,118.368103</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>117.278511,117.025917,116.848923,116.801971,116.545464,116.403076,116.469818,116.351105,116.135391,115.895004,115.863647,115.739868,115.771873,115.434425,115.505867,115.415207,115.391525,115.280830,114.733986,114.533920,114.558670,114.373749,114.294388,114.398033</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>117.766792,117.570854,117.493355,117.447365,117.316635,117.160889,117.324059,117.157890,117.120659,116.810425,116.689827,116.867592,116.808716,116.504318,116.675095,116.614388,116.682434,116.330788,116.144760,116.013824,115.920898,115.811295,115.865517,115.775406</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>118.5425415039062</v>
+      </c>
+      <c r="G74" t="n">
+        <v>119.1399993896484</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.5974578857422443</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.5014754816207888</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.7136719306384726</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:42</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>119.1118240356445</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>118.402260,118.368950,118.425438,118.482544,118.428398,118.450348,118.574562,118.514725,118.467888,118.465584,118.408791,118.552086,118.557625,118.535088,118.666679,118.651779,118.794456,118.707451,118.668823,118.694878,118.674507,118.639069,118.531509,118.542542</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>118.050003,118.430000,118.169998,119.279999,119.830002,119.459999,121.870003,121.010002,118.779999,119.260002,120.269997,119.150002,118.669998,117.180000,117.980003,118.000000,118.099998,118.059998,117.940002,118.029999,118.120003,118.589996,119.029999,119.139999</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.352257,0.061050,0.255440,0.797455,1.401604,1.009651,3.295441,2.495277,0.312111,0.794418,1.861206,0.597916,0.112373,1.355088,0.686676,0.651779,0.694458,0.647453,0.728821,0.664879,0.554504,0.049073,0.498490,0.597457</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.298396,0.051550,0.216163,0.668557,1.169660,0.845179,2.704062,2.062042,0.262764,0.666123,1.547523,0.501817,0.094694,1.156416,0.582027,0.552355,0.588025,0.548411,0.617959,0.563314,0.469441,0.041380,0.418793,0.501475</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.7136719306384726</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>118.132370,118.465988,118.315414,118.274063,118.508316,118.434975,118.526360,118.280815,118.372528,118.620651,118.374275,118.350983,118.344482,118.546280,118.710182,118.512497,118.643143,118.566086,118.696579,118.250603,118.454399,118.373131,118.520584,118.368103</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>117.766792,117.570854,117.493355,117.447365,117.316635,117.160889,117.324059,117.157890,117.120659,116.810425,116.689827,116.867592,116.808716,116.504318,116.675095,116.614388,116.682434,116.330788,116.144760,116.013824,115.920898,115.811295,115.865517,115.775406</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:42</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>119.087677,119.035141,119.078011,119.138176,119.172684,119.136841,119.278603,119.198029,119.144463,119.178688,119.145378,119.123863,119.174629,119.100281,119.183495,119.062744,119.218781,119.180702,119.139008,119.215729,119.100319,119.074867,119.087517,119.111824</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>118.951645,118.982147,119.080734,118.927238,119.277199,119.182693,119.309639,119.067924,118.987663,119.046608,119.013702,118.930748,118.901543,118.977409,119.115150,118.739700,118.975731,118.932404,119.195564,118.819977,118.813683,118.822319,118.953674,118.924698</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>118.084076,117.744583,117.514915,117.488655,117.275192,117.077370,117.097366,116.845650,116.736511,116.642464,116.569092,116.242043,116.293823,115.994263,116.047478,115.780182,115.832016,115.759949,115.295540,115.213257,115.142387,115.009918,115.031532,114.970551</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>118.498360,118.247398,118.136536,118.086868,117.950294,117.737335,117.866714,117.697708,117.665535,117.501755,117.382103,117.388733,117.425781,117.048531,117.189468,117.022034,117.154930,116.932930,116.764297,116.724411,116.535645,116.521530,116.603355,116.520554</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>119.1118240356445</v>
+      </c>
+      <c r="G75" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.788177490234403</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3.082325014810298</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.196632313800403</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:18</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>123.3136138916016</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>119.087677,119.035141,119.078011,119.138176,119.172684,119.136841,119.278603,119.198029,119.144463,119.178688,119.145378,119.123863,119.174629,119.100281,119.183495,119.062744,119.218781,119.180702,119.139008,119.215729,119.100319,119.074867,119.087517,119.111824</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>119.169998,117.430000,117.849998,117.650002,117.959999,117.919998,117.309998,117.970001,117.349998,117.320000,117.080002,118.330002,118.349998,118.190002,118.110001,117.629997,118.279999,118.379997,118.839996,119.480003,120.019997,121.190002,123.430000,122.900002</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.082321,1.605141,1.228013,1.488174,1.212685,1.216843,1.968605,1.228028,1.794465,1.858688,2.065376,0.793861,0.824631,0.910279,1.073494,1.432747,0.938782,0.800705,0.299012,0.264274,0.919678,2.115135,4.342483,3.788178</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.069079,1.366892,1.042013,1.264917,1.028048,1.031922,1.678122,1.040966,1.529156,1.584289,1.764073,0.670887,0.696773,0.770182,0.908894,1.218011,0.793695,0.676385,0.251609,0.221187,0.766270,1.745305,3.518175,3.082325</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1.196632313800403</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>118.951645,118.982147,119.080734,118.927238,119.277199,119.182693,119.309639,119.067924,118.987663,119.046608,119.013702,118.930748,118.901543,118.977409,119.115150,118.739700,118.975731,118.932404,119.195564,118.819977,118.813683,118.822319,118.953674,118.924698</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>118.498360,118.247398,118.136536,118.086868,117.950294,117.737335,117.866714,117.697708,117.665535,117.501755,117.382103,117.388733,117.425781,117.048531,117.189468,117.022034,117.154930,116.932930,116.764297,116.724411,116.535645,116.521530,116.603355,116.520554</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:18</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>122.682808,122.710129,122.868507,122.930466,123.064575,123.090385,123.272446,123.281700,123.385483,123.366882,123.456001,123.429276,123.453896,123.314682,123.342041,123.271721,123.380203,123.296463,123.227989,123.238495,123.246323,123.252609,123.248062,123.313614</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>122.572647,122.705933,122.865723,122.828949,122.978233,123.146423,123.109756,123.171471,123.148613,123.410339,123.368484,123.225273,123.115822,123.222351,123.143776,123.024902,123.000595,123.104362,123.090698,122.781250,122.861107,123.004921,123.173523,123.026253</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>121.469398,121.235687,121.097076,120.997223,120.923431,120.704880,120.737869,120.573479,120.518326,120.264488,120.273682,120.078011,120.068069,119.589302,119.517273,119.387817,119.436554,119.333305,118.928719,118.730133,118.715828,118.485542,118.452026,118.575096</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>121.945587,121.747162,121.734314,121.688744,121.597763,121.411400,121.585716,121.416260,121.535774,121.278374,121.204758,121.247009,121.242844,120.786148,120.811348,120.777962,120.878464,120.599297,120.383125,120.302368,120.180946,120.066109,120.113327,120.161179</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>123.3136138916016</v>
+      </c>
+      <c r="G76" t="n">
+        <v>119.0800018310547</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4.233612060546918</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3.555267043540505</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.718084077689111</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>119.0041351318359</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>122.682808,122.710129,122.868507,122.930466,123.064575,123.090385,123.272446,123.281700,123.385483,123.366882,123.456001,123.429276,123.453896,123.314682,123.342041,123.271721,123.380203,123.296463,123.227989,123.238495,123.246323,123.252609,123.248062,123.313614</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>121.720001,121.680000,122.029999,121.760002,121.889999,121.800003,122.540001,122.050003,120.610001,119.949997,119.959999,119.690002,118.120003,117.949997,117.769997,118.190002,118.510002,118.580002,118.959999,119.110001,118.889999,119.389999,119.150002,119.080002</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.962807,1.030129,0.838508,1.170464,1.174576,1.290382,0.732445,1.231697,2.775482,3.416885,3.496002,3.739274,5.333893,5.364685,5.572044,5.081719,4.870201,4.716461,4.267990,4.128494,4.356324,3.862610,4.098060,4.233612</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.791001,0.846588,0.687133,0.961288,0.963636,1.059427,0.597719,1.009174,2.301204,2.848591,2.914306,3.124132,4.515656,4.548271,4.731294,4.299618,4.109527,3.977451,3.587752,3.466119,3.664163,3.235287,3.439413,3.555267</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2.718084077689111</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>122.572647,122.705933,122.865723,122.828949,122.978233,123.146423,123.109756,123.171471,123.148613,123.410339,123.368484,123.225273,123.115822,123.222351,123.143776,123.024902,123.000595,123.104362,123.090698,122.781250,122.861107,123.004921,123.173523,123.026253</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>121.945587,121.747162,121.734314,121.688744,121.597763,121.411400,121.585716,121.416260,121.535774,121.278374,121.204758,121.247009,121.242844,120.786148,120.811348,120.777962,120.878464,120.599297,120.383125,120.302368,120.180946,120.066109,120.113327,120.161179</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>119.134514,119.082710,119.076805,119.083382,119.034157,119.010513,119.119606,119.030434,119.041496,119.009270,119.015556,119.013435,118.974365,118.886818,118.967278,118.916283,119.005997,119.025322,119.035980,119.048813,119.026131,119.021362,118.998795,119.004135</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>119.021004,119.134575,119.011024,119.003052,119.031654,119.099396,119.069580,118.886307,119.004028,119.058647,118.991837,118.856056,118.743439,118.897087,118.825607,118.681114,118.722740,118.865616,118.849785,118.762047,118.826164,118.737663,118.990822,118.877495</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>118.242683,117.961906,117.716866,117.625282,117.273308,117.128113,117.166969,116.882126,116.765129,116.556480,116.460655,116.309250,116.217613,115.936340,115.873848,115.726395,115.670044,115.669815,115.242043,115.177109,115.154243,115.032173,114.966927,114.971207</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>118.617691,118.374046,118.190979,118.091881,117.861053,117.692474,117.798843,117.583359,117.653107,117.421486,117.263687,117.224899,117.215919,116.885788,116.957298,116.858253,116.898582,116.709015,116.592712,116.558723,116.524490,116.394333,116.445374,116.404411</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>119.0041351318359</v>
+      </c>
+      <c r="G77" t="n">
+        <v>120.7399978637695</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.735862731933636</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.437686568366684</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.6512708087161145</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>121.0434494018555</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>119.134514,119.082710,119.076805,119.083382,119.034157,119.010513,119.119606,119.030434,119.041496,119.009270,119.015556,119.013435,118.974365,118.886818,118.967278,118.916283,119.005997,119.025322,119.035980,119.048813,119.026131,119.021362,118.998795,119.004135</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>119.430000,119.320000,119.269997,119.309998,119.480003,119.300003,119.459999,119.410004,119.760002,119.680000,119.699997,119.980003,119.919998,119.779999,119.790001,119.629997,119.699997,119.589996,120.169998,120.129997,120.400002,120.760002,120.620003,120.739998</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.295486,0.237290,0.193192,0.226616,0.445846,0.289490,0.340393,0.379570,0.718506,0.670730,0.684441,0.966568,0.945633,0.893181,0.822723,0.713714,0.694000,0.564674,1.134018,1.081184,1.373871,1.738640,1.621208,1.735863</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.247414,0.198868,0.161978,0.189938,0.373156,0.242657,0.284943,0.317871,0.599955,0.560436,0.571797,0.805608,0.788553,0.745684,0.686804,0.596601,0.579783,0.472175,0.943678,0.900012,1.141088,1.439748,1.344062,1.437687</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.6512708087161145</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>119.021004,119.134575,119.011024,119.003052,119.031654,119.099396,119.069580,118.886307,119.004028,119.058647,118.991837,118.856056,118.743439,118.897087,118.825607,118.681114,118.722740,118.865616,118.849785,118.762047,118.826164,118.737663,118.990822,118.877495</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>118.617691,118.374046,118.190979,118.091881,117.861053,117.692474,117.798843,117.583359,117.653107,117.421486,117.263687,117.224899,117.215919,116.885788,116.957298,116.858253,116.898582,116.709015,116.592712,116.558723,116.524490,116.394333,116.445374,116.404411</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>120.712189,120.769096,120.797508,120.934990,120.905144,120.953712,121.121933,121.004219,121.033005,121.043900,120.990051,121.033653,120.898895,120.854774,120.857773,120.886993,120.995926,120.896355,121.020584,120.972519,120.980171,121.018684,120.995232,121.043449</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>120.599670,120.751694,120.739632,120.918602,120.934868,120.906204,121.071152,120.962914,120.951500,121.076820,120.945496,120.806564,120.689262,120.732529,120.592537,120.591141,120.642204,120.711166,120.908348,120.659821,120.717346,120.789688,120.848679,120.944153</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>119.952690,119.836594,119.756523,119.899590,119.499336,119.535942,119.519699,119.226860,119.170494,118.965797,118.786720,118.696968,118.546913,118.411751,118.265976,118.253944,118.280472,118.130356,117.821106,117.674500,117.714592,117.637695,117.563309,117.633072</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>120.310242,120.211555,120.186752,120.245430,120.071587,119.942871,120.049133,119.865150,119.977180,119.718475,119.536888,119.473991,119.418739,119.227325,119.139198,119.208076,119.396790,119.032097,119.037354,118.912003,118.846077,118.746086,118.800926,118.760277</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>121.0434494018555</v>
+      </c>
+      <c r="G78" t="n">
+        <v>120.1699981689453</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.8734512329101847</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.726846339534941</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.3609896687464806</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:14</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>119.7287979125977</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>120.712189,120.769096,120.797508,120.934990,120.905144,120.953712,121.121933,121.004219,121.033005,121.043900,120.990051,121.033653,120.898895,120.854774,120.857773,120.886993,120.995926,120.896355,121.020584,120.972519,120.980171,121.018684,120.995232,121.043449</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>120.940002,121.110001,120.940002,121.290001,121.260002,121.220001,121.279999,121.699997,121.839996,121.540001,121.720001,121.470001,121.459999,121.080002,121.239998,121.169998,121.709999,121.570000,121.300003,121.139999,121.169998,120.400002,120.470001,120.169998</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.227813,0.340905,0.142494,0.355011,0.354858,0.266289,0.158066,0.695778,0.806991,0.496101,0.729950,0.436348,0.561104,0.225228,0.382225,0.283005,0.714073,0.673645,0.279419,0.167480,0.189827,0.618682,0.525231,0.873451</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.188369,0.281483,0.117822,0.292696,0.292642,0.219674,0.130331,0.571716,0.662337,0.408179,0.599696,0.359223,0.461966,0.186016,0.315263,0.233560,0.586700,0.554121,0.230354,0.138254,0.156662,0.513856,0.435985,0.726846</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.3609896687464806</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>120.599670,120.751694,120.739632,120.918602,120.934868,120.906204,121.071152,120.962914,120.951500,121.076820,120.945496,120.806564,120.689262,120.732529,120.592537,120.591141,120.642204,120.711166,120.908348,120.659821,120.717346,120.789688,120.848679,120.944153</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>120.310242,120.211555,120.186752,120.245430,120.071587,119.942871,120.049133,119.865150,119.977180,119.718475,119.536888,119.473991,119.418739,119.227325,119.139198,119.208076,119.396790,119.032097,119.037354,118.912003,118.846077,118.746086,118.800926,118.760277</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:14</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>120.087944,119.986443,119.871292,119.885460,119.779846,119.800117,119.889923,119.773483,119.748131,119.809097,119.716858,119.805641,119.670227,119.661201,119.722237,119.763008,119.823906,119.747482,119.748444,119.735634,119.765907,119.756218,119.747215,119.728798</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>119.964584,120.036209,119.782936,119.845573,119.892265,119.751228,119.841347,119.713120,119.716492,119.873657,119.689705,119.613556,119.506210,119.558723,119.433777,119.536598,119.596291,119.385071,119.657394,119.424545,119.565239,119.492142,119.488235,119.662178</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>119.398216,119.234444,118.994713,118.957130,118.620880,118.599945,118.545120,118.301476,118.220535,118.063164,117.922211,117.861679,117.775711,117.725746,117.660255,117.556290,117.519455,117.346863,117.022217,116.917641,116.976196,116.902870,116.903244,116.888275</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>119.733780,119.541199,119.370583,119.272278,119.050743,118.975555,119.012016,118.836609,118.919647,118.683891,118.513451,118.557411,118.476540,118.392952,118.428940,118.414696,118.528435,118.203819,118.179214,118.065033,118.089188,117.995331,118.057312,117.908073</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>119.7287979125977</v>
+      </c>
+      <c r="G79" t="n">
+        <v>119.7799987792969</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.05120086669917612</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.04274575657119294</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.6151794701256347</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:21</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>119.5295944213867</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>120.087944,119.986443,119.871292,119.885460,119.779846,119.800117,119.889923,119.773483,119.748131,119.809097,119.716858,119.805641,119.670227,119.661201,119.722237,119.763008,119.823906,119.747482,119.748444,119.735634,119.765907,119.756218,119.747215,119.728798</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>121.550003,121.660004,121.029999,120.610001,120.650002,120.809998,120.339996,120.790001,119.489998,119.320000,119.599998,120.010002,120.089996,120.269997,120.639999,120.800003,121.040001,120.769997,121.019997,120.620003,120.190002,119.980003,120.070000,119.779999</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.462059,1.673561,1.158707,0.724541,0.870156,1.009881,0.450073,1.016518,0.258133,0.489097,0.116860,0.204361,0.419769,0.608796,0.917762,1.036995,1.216095,1.022515,1.271553,0.884369,0.424095,0.223785,0.322785,0.051201</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.202846,1.375605,0.957372,0.600730,0.721223,0.835925,0.374001,0.841558,0.216029,0.409904,0.097709,0.170287,0.349546,0.506191,0.760745,0.858440,1.004705,0.846663,1.050696,0.733186,0.352854,0.186519,0.268830,0.042746</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.6151794701256347</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>119.964584,120.036209,119.782936,119.845573,119.892265,119.751228,119.841347,119.713120,119.716492,119.873657,119.689705,119.613556,119.506210,119.558723,119.433777,119.536598,119.596291,119.385071,119.657394,119.424545,119.565239,119.492142,119.488235,119.662178</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>119.733780,119.541199,119.370583,119.272278,119.050743,118.975555,119.012016,118.836609,118.919647,118.683891,118.513451,118.557411,118.476540,118.392952,118.428940,118.414696,118.528435,118.203819,118.179214,118.065033,118.089188,117.995331,118.057312,117.908073</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:21</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>119.436935,119.382309,119.348869,119.410690,119.346001,119.373550,119.483948,119.313156,119.327095,119.414566,119.339264,119.390457,119.350555,119.365425,119.410843,119.489830,119.542877,119.484985,119.485802,119.522537,119.547623,119.542595,119.520058,119.529594</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>119.360809,119.526329,119.300621,119.422195,119.416382,119.407196,119.506355,119.320305,119.301346,119.403191,119.406296,119.305489,119.229744,119.410675,119.345863,119.238960,119.441917,119.350006,119.486137,119.225258,119.423729,119.270020,119.368103,119.487595</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>118.872925,118.679565,118.460503,118.455544,118.191711,118.073441,118.124146,117.780563,117.669060,117.591629,117.432930,117.379898,117.242554,117.178192,117.128784,117.043137,117.070366,116.957825,116.568489,116.506416,116.525696,116.403145,116.321510,116.346817</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>119.157074,118.976738,118.836433,118.808350,118.626175,118.526344,118.580772,118.372742,118.402824,118.251686,118.051804,118.119400,118.079697,117.966461,118.012482,118.006821,118.116989,117.889664,117.813072,117.777222,117.784210,117.650681,117.612244,117.558952</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>119.5295944213867</v>
+      </c>
+      <c r="G80" t="n">
+        <v>118.5699996948242</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9595947265624858</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.8093065101056703</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9842052186448161</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:33</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>118.6899490356445</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>119.436935,119.382309,119.348869,119.410690,119.346001,119.373550,119.483948,119.313156,119.327095,119.414566,119.339264,119.390457,119.350555,119.365425,119.410843,119.489830,119.542877,119.484985,119.485802,119.522537,119.547623,119.542595,119.520058,119.529594</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>120.209999,120.459999,119.519997,120.209999,120.320000,120.430000,120.879997,121.760002,120.489998,120.269997,120.849998,120.839996,120.790001,120.989998,121.010002,120.820000,120.690002,120.570000,118.970001,118.269997,118.220001,118.050003,118.570000,118.570000</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.773064,1.077690,0.171128,0.799309,0.973999,1.056450,1.396049,2.446846,1.162903,0.855431,1.510734,1.449539,1.439446,1.624573,1.599159,1.330170,1.147125,1.085015,0.515801,1.252540,1.327622,1.492592,0.950058,0.959594</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.643095,0.894646,0.143179,0.664927,0.809507,0.877232,1.154905,2.009565,0.965145,0.711259,1.250091,1.199553,1.191693,1.342733,1.321510,1.100952,0.950473,0.899904,0.433555,1.059052,1.123009,1.264373,0.801264,0.809306</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9842052186448161</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>119.360809,119.526329,119.300621,119.422195,119.416382,119.407196,119.506355,119.320305,119.301346,119.403191,119.406296,119.305489,119.229744,119.410675,119.345863,119.238960,119.441917,119.350006,119.486137,119.225258,119.423729,119.270020,119.368103,119.487595</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>119.157074,118.976738,118.836433,118.808350,118.626175,118.526344,118.580772,118.372742,118.402824,118.251686,118.051804,118.119400,118.079697,117.966461,118.012482,118.006821,118.116989,117.889664,117.813072,117.777222,117.784210,117.650681,117.612244,117.558952</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:33</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>118.634377,118.578140,118.520569,118.615631,118.575401,118.650024,118.712845,118.516487,118.514679,118.593140,118.521591,118.570808,118.573875,118.579460,118.591850,118.683708,118.759399,118.736526,118.678635,118.700706,118.688797,118.615845,118.713852,118.689949</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>118.550125,118.778526,118.549141,118.681534,118.715981,118.727928,118.875374,118.579781,118.572739,118.585266,118.606628,118.578659,118.635376,118.750526,118.607750,118.462463,118.687157,118.781227,118.783157,118.434746,118.620583,118.318130,118.610054,118.724060</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>117.762428,117.559074,117.333321,117.330185,117.114967,117.048233,117.043907,116.640358,116.542770,116.445732,116.318001,116.293541,116.170868,116.084473,116.068810,115.983185,116.018425,115.931686,115.507927,115.450607,115.476715,115.334015,115.349632,115.292587</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>118.162079,117.945343,117.750465,117.794350,117.641464,117.593323,117.594833,117.331329,117.345779,117.223808,117.012680,117.104881,117.065971,116.914482,116.971176,116.996758,117.047821,116.917480,116.785866,116.750557,116.728760,116.591133,116.651718,116.543640</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>118.6899490356445</v>
+      </c>
+      <c r="G81" t="n">
+        <v>115.3099975585938</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.379951477050753</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.931186842956319</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.8122057789684</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:49</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>114.9599456787109</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>118.634377,118.578140,118.520569,118.615631,118.575401,118.650024,118.712845,118.516487,118.514679,118.593140,118.521591,118.570808,118.573875,118.579460,118.591850,118.683708,118.759399,118.736526,118.678635,118.700706,118.688797,118.615845,118.713852,118.689949</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>118.779999,118.580002,118.190002,117.739998,117.620003,117.320000,116.360001,116.169998,115.830002,116.720001,116.750000,116.300003,116.070000,115.820000,116.150002,115.540001,115.949997,116.250000,116.360001,116.019997,116.419998,115.660004,114.919998,115.309998</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.145622,0.001862,0.330567,0.875633,0.955398,1.330024,2.352844,2.346489,2.684677,1.873139,1.771591,2.270805,2.503875,2.759460,2.441848,3.143707,2.809402,2.486526,2.318634,2.680709,2.268799,2.955841,3.793854,3.379951</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.122598,0.001570,0.279691,0.743701,0.812275,1.133672,2.022039,2.019875,2.317774,1.604814,1.517423,1.952541,2.157211,2.382542,2.102323,2.720882,2.422943,2.138947,1.992639,2.310558,1.948805,2.555630,3.301300,2.931187</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.8122057789684</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>118.550125,118.778526,118.549141,118.681534,118.715981,118.727928,118.875374,118.579781,118.572739,118.585266,118.606628,118.578659,118.635376,118.750526,118.607750,118.462463,118.687157,118.781227,118.783157,118.434746,118.620583,118.318130,118.610054,118.724060</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>118.162079,117.945343,117.750465,117.794350,117.641464,117.593323,117.594833,117.331329,117.345779,117.223808,117.012680,117.104881,117.065971,116.914482,116.971176,116.996758,117.047821,116.917480,116.785866,116.750557,116.728760,116.591133,116.651718,116.543640</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:49</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>115.227119,115.188850,115.167397,115.169823,115.144592,115.194405,115.227402,115.122353,115.161568,115.140778,115.112511,115.157997,115.160721,115.201424,115.246422,115.170135,115.263458,115.226791,115.195084,115.155418,115.137756,115.011414,115.095001,114.959946</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>114.987160,115.424263,115.281364,115.201797,115.282234,115.309425,115.349823,115.072083,115.217537,115.333298,115.205078,115.403091,115.452209,115.518951,115.504814,115.100616,115.431038,115.603378,115.595642,115.194344,115.266731,114.956024,115.192245,115.209457</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>114.471901,114.278564,114.005280,113.901093,113.786896,113.640831,113.644012,113.432831,113.189522,112.906219,112.751549,112.747185,112.648621,112.466415,112.507942,112.141510,112.213219,112.000755,111.540016,111.454597,111.428612,111.164406,111.176567,110.942955</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>114.830948,114.610565,114.428024,114.342506,114.234222,114.189903,114.177063,114.020798,114.078979,113.721809,113.548851,113.562538,113.639885,113.432487,113.528877,113.299812,113.408577,113.066261,113.041306,112.972603,112.922028,112.554306,112.724487,112.496857</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>114.9599456787109</v>
+      </c>
+      <c r="G82" t="n">
+        <v>110.2699966430664</v>
+      </c>
+      <c r="H82" t="n">
+        <v>4.689949035644489</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4.253150610700943</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.825371736693576</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:52</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>110.5532150268555</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>115.227119,115.188850,115.167397,115.169823,115.144592,115.194405,115.227402,115.122353,115.161568,115.140778,115.112511,115.157997,115.160721,115.201424,115.246422,115.170135,115.263458,115.226791,115.195084,115.155418,115.137756,115.011414,115.095001,114.959946</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>115.279999,114.870003,114.809998,115.099998,114.339996,113.070000,112.419998,112.180000,112.430000,108.470001,107.629997,106.300003,108.019997,109.080002,109.830002,110.550003,110.279999,109.540001,109.250000,109.349998,110.230003,110.330002,109.820000,110.269997</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.052880,0.318847,0.357399,0.069825,0.804596,2.124405,2.807404,2.942353,2.731568,6.670777,7.482514,8.857994,7.140724,6.121422,5.416420,4.620132,4.983459,5.686790,5.945084,5.805420,4.907753,4.681412,5.275001,4.689949</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.045871,0.277572,0.311296,0.060664,0.703687,1.878841,2.497246,2.622885,2.429572,6.149882,6.952071,8.333014,6.610558,5.611865,4.931640,4.179224,4.518915,5.191519,5.441724,5.309026,4.452284,4.243100,4.803316,4.253151</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3.825371736693576</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>114.987160,115.424263,115.281364,115.201797,115.282234,115.309425,115.349823,115.072083,115.217537,115.333298,115.205078,115.403091,115.452209,115.518951,115.504814,115.100616,115.431038,115.603378,115.595642,115.194344,115.266731,114.956024,115.192245,115.209457</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>114.830948,114.610565,114.428024,114.342506,114.234222,114.189903,114.177063,114.020798,114.078979,113.721809,113.548851,113.562538,113.639885,113.432487,113.528877,113.299812,113.408577,113.066261,113.041306,112.972603,112.922028,112.554306,112.724487,112.496857</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:52</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>110.296707,110.290375,110.300865,110.379456,110.435768,110.402290,110.322456,110.363266,110.368950,110.321930,110.260048,110.286781,110.315407,110.369179,110.427368,110.387909,110.502846,110.521301,110.515785,110.540230,110.546768,110.475487,110.482300,110.553215</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>110.316132,110.438698,110.380119,110.404137,110.509956,110.406494,110.527977,110.245178,110.659599,110.387833,110.396301,110.468620,110.580544,110.592552,110.671471,110.565147,110.908089,110.913780,111.014320,110.531921,110.831902,110.405624,110.759857,110.679466</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>109.102097,108.693939,108.336754,108.173203,107.876976,107.580818,107.371849,107.218750,106.926537,106.719345,106.434204,106.388962,106.343704,106.133171,106.211670,106.009125,106.078888,105.842369,105.406952,105.347847,105.113945,105.060738,105.034210,104.899948</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>109.638054,109.341293,109.107307,108.931595,108.759201,108.608406,108.327873,108.225822,108.302734,108.019157,107.711258,107.712952,107.705734,107.554512,107.689720,107.506508,107.675430,107.355217,107.369621,107.352112,107.222755,106.896530,107.116516,107.045830</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>110.5532150268555</v>
+      </c>
+      <c r="G83" t="n">
+        <v>110.0400009155273</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.5132141113281534</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.4663886832590308</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7208883835753634</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:14</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>110.0468063354492</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>110.296707,110.290375,110.300865,110.379456,110.435768,110.402290,110.322456,110.363266,110.368950,110.321930,110.260048,110.286781,110.315407,110.369179,110.427368,110.387909,110.502846,110.521301,110.515785,110.540230,110.546768,110.475487,110.482300,110.553215</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>110.550003,110.599998,110.540001,110.300003,109.680000,111.220001,110.339996,109.500000,109.989998,109.639999,109.680000,109.790001,109.379997,108.379997,108.940002,108.940002,109.110001,109.040001,109.290001,109.860001,109.830002,109.599998,109.769997,110.040001</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.253296,0.309623,0.239136,0.079453,0.755768,0.817711,0.017540,0.863266,0.378952,0.681931,0.580048,0.496780,0.935410,1.989182,1.487366,1.447907,1.392845,1.481300,1.225784,0.680229,0.716766,0.875489,0.712303,0.513214</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.229124,0.279949,0.216334,0.072033,0.689066,0.735220,0.015897,0.788371,0.344533,0.621972,0.528855,0.452482,0.855193,1.835377,1.365307,1.329086,1.276552,1.358492,1.121589,0.619178,0.652614,0.798803,0.648905,0.466389</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.7208883835753634</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>110.316132,110.438698,110.380119,110.404137,110.509956,110.406494,110.527977,110.245178,110.659599,110.387833,110.396301,110.468620,110.580544,110.592552,110.671471,110.565147,110.908089,110.913780,111.014320,110.531921,110.831902,110.405624,110.759857,110.679466</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>109.638054,109.341293,109.107307,108.931595,108.759201,108.608406,108.327873,108.225822,108.302734,108.019157,107.711258,107.712952,107.705734,107.554512,107.689720,107.506508,107.675430,107.355217,107.369621,107.352112,107.222755,106.896530,107.116516,107.045830</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:14</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>110.155861,110.136093,110.153229,110.136856,110.128540,110.085854,110.038673,110.003136,109.918022,109.874763,109.844124,109.846245,109.872505,109.872368,109.963524,109.956451,109.923012,109.944748,109.942871,110.010361,110.009834,109.987640,109.946411,110.046806</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>110.216339,110.248505,110.039719,110.133011,110.174263,110.161964,110.112930,109.747581,110.053490,109.878036,109.850319,109.907852,110.027306,110.126610,110.111351,109.894424,110.136665,110.182320,110.232338,110.048820,110.119751,109.953903,110.089478,110.077133</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>109.131340,108.860519,108.612442,108.524193,108.278824,108.091454,108.006386,107.792374,107.399437,107.262352,107.074677,107.027161,106.904900,106.715622,106.815353,106.561096,106.525620,106.315964,105.956863,106.007019,105.802147,105.771317,105.683197,105.545563</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>109.615150,109.357178,109.172691,109.054726,108.899605,108.798615,108.661491,108.476509,108.445816,108.235832,108.017731,107.986244,107.974594,107.838409,107.997627,107.846405,107.800003,107.525291,107.535545,107.617813,107.478745,107.286919,107.366829,107.297935</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>110.0468063354492</v>
+      </c>
+      <c r="G84" t="n">
+        <v>109.6100006103516</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.436805725097642</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.3985090070845143</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.2930624929227524</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>109.2330932617188</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>110.155861,110.136093,110.153229,110.136856,110.128540,110.085854,110.038673,110.003136,109.918022,109.874763,109.844124,109.846245,109.872505,109.872368,109.963524,109.956451,109.923012,109.944748,109.942871,110.010361,110.009834,109.987640,109.946411,110.046806</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>109.730003,109.849998,109.910004,109.839996,109.589996,109.769997,109.650002,109.830002,110.400002,110.370003,109.949997,109.860001,110.190002,110.339996,110.250000,110.209999,110.379997,109.980003,109.800003,109.940002,109.910004,109.050003,109.489998,109.610001</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.425858,0.286095,0.243225,0.296860,0.538544,0.315857,0.388671,0.173134,0.481980,0.495240,0.105873,0.013756,0.317497,0.467628,0.286476,0.253548,0.456985,0.035255,0.142868,0.070359,0.099830,0.937637,0.456413,0.436805</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.388096,0.260441,0.221295,0.270266,0.491417,0.287745,0.354466,0.157638,0.436576,0.448709,0.096292,0.012521,0.288136,0.423807,0.259842,0.230059,0.414011,0.032056,0.130117,0.063997,0.090829,0.859823,0.416854,0.398509</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.2930624929227524</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>110.216339,110.248505,110.039719,110.133011,110.174263,110.161964,110.112930,109.747581,110.053490,109.878036,109.850319,109.907852,110.027306,110.126610,110.111351,109.894424,110.136665,110.182320,110.232338,110.048820,110.119751,109.953903,110.089478,110.077133</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>109.615150,109.357178,109.172691,109.054726,108.899605,108.798615,108.661491,108.476509,108.445816,108.235832,108.017731,107.986244,107.974594,107.838409,107.997627,107.846405,107.800003,107.525291,107.535545,107.617813,107.478745,107.286919,107.366829,107.297935</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>109.676132,109.675758,109.620438,109.562592,109.604515,109.560677,109.514404,109.477043,109.405998,109.399292,109.391808,109.343529,109.313187,109.338493,109.365776,109.289581,109.293953,109.297607,109.271149,109.277908,109.226662,109.261810,109.164520,109.233093</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>109.704376,109.688499,109.565346,109.541298,109.584175,109.474174,109.550949,109.286423,109.479149,109.473618,109.265816,109.300377,109.466095,109.377838,109.448227,109.291710,109.452232,109.361603,109.390511,109.415573,109.386604,109.285004,109.101364,109.214493</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>108.919418,108.710052,108.445602,108.367317,108.254951,108.144760,108.092834,107.962166,107.707108,107.651306,107.461411,107.375595,107.179596,107.208595,107.112778,106.879189,106.841187,106.705124,106.430870,106.413467,106.210587,106.278313,106.088257,105.952759</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>109.278824,109.092712,108.905319,108.800652,108.764748,108.715454,108.563988,108.503571,108.513802,108.351364,108.210503,108.101440,108.072807,108.062576,108.092392,107.890244,107.882591,107.710281,107.657043,107.684410,107.518204,107.436356,107.347946,107.329468</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>109.2330932617188</v>
+      </c>
+      <c r="G85" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.266906738281193</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.903917100694394</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.379058420695315</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:33</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>112.3570022583008</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>109.676132,109.675758,109.620438,109.562592,109.604515,109.560677,109.514404,109.477043,109.405998,109.399292,109.391808,109.343529,109.313187,109.338493,109.365776,109.289581,109.293953,109.297607,109.271149,109.277908,109.226662,109.261810,109.164520,109.233093</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>109.720001,109.300003,109.400002,109.389999,109.230003,109.489998,109.410004,109.349998,109.650002,111.830002,112.199997,112.010002,111.430000,111.239998,111.220001,110.620003,110.949997,111.209999,111.500000,111.489998,111.910004,111.559998,113.029999,112.500000</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.043869,0.375755,0.220436,0.172593,0.374512,0.070679,0.104400,0.127045,0.244004,2.430710,2.808189,2.666473,2.116813,1.901505,1.854225,1.330422,1.656044,1.912392,2.228851,2.212090,2.683342,2.298188,3.865479,3.266907</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.039983,0.343783,0.201496,0.157777,0.342865,0.064553,0.095421,0.116182,0.222529,2.173576,2.502842,2.380567,1.899680,1.709372,1.667169,1.202695,1.492604,1.719622,1.998970,1.984115,2.397767,2.060046,3.419870,2.903917</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.379058420695315</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>109.704376,109.688499,109.565346,109.541298,109.584175,109.474174,109.550949,109.286423,109.479149,109.473618,109.265816,109.300377,109.466095,109.377838,109.448227,109.291710,109.452232,109.361603,109.390511,109.415573,109.386604,109.285004,109.101364,109.214493</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>109.278824,109.092712,108.905319,108.800652,108.764748,108.715454,108.563988,108.503571,108.513802,108.351364,108.210503,108.101440,108.072807,108.062576,108.092392,107.890244,107.882591,107.710281,107.657043,107.684410,107.518204,107.436356,107.347946,107.329468</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:33</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>112.524651,112.525291,112.531990,112.551285,112.615234,112.611649,112.649750,112.636604,112.649757,112.586884,112.631210,112.591431,112.595520,112.536247,112.594635,112.510681,112.525574,112.467041,112.390503,112.426315,112.360527,112.332886,112.320488,112.357002</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>112.671333,112.541954,112.519447,112.501617,112.480171,112.507729,112.627769,112.589890,112.613007,112.535782,112.499390,112.460365,112.634819,112.570984,112.610603,112.520454,112.576073,112.355339,112.425179,112.477814,112.384171,112.392929,112.212700,112.290840</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>111.477562,111.169479,110.877495,110.820160,110.639030,110.522774,110.481796,110.408180,110.244644,110.132378,110.047363,109.981659,109.821831,109.773277,109.728912,109.455383,109.391647,109.248344,108.856720,108.863960,108.748177,108.747246,108.642815,108.503998</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>111.952209,111.714233,111.495110,111.470863,111.351036,111.276176,111.214386,111.213593,111.212090,111.040108,110.992744,110.893326,110.889915,110.798561,110.805367,110.614540,110.605461,110.411453,110.236740,110.331696,110.142059,110.075180,110.043686,110.067162</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>112.3570022583008</v>
+      </c>
+      <c r="G86" t="n">
+        <v>108.3600006103516</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.997001647949233</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3.688631990988935</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.703358134636017</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:48</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>108.6364669799805</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>112.524651,112.525291,112.531990,112.551285,112.615234,112.611649,112.649750,112.636604,112.649757,112.586884,112.631210,112.591431,112.595520,112.536247,112.594635,112.510681,112.525574,112.467041,112.390503,112.426315,112.360527,112.332886,112.320488,112.357002</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>112.540001,112.480003,111.610001,111.629997,111.540001,110.910004,110.139999,110.379997,108.669998,108.779999,107.709999,107.650002,107.430000,108.190002,108.339996,107.089996,106.300003,105.629997,102.830002,105.230003,106.629997,107.349998,107.949997,108.360001</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.015350,0.045288,0.921989,0.921288,1.075233,1.701645,2.509751,2.256607,3.979759,3.806885,4.921211,4.941429,5.165520,4.346245,4.254639,5.420685,6.225571,6.837044,9.560501,7.196312,5.730530,4.982888,4.370491,3.997001</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.013640,0.040263,0.826081,0.825305,0.963989,1.534258,2.278691,2.044398,3.662242,3.499619,4.568945,4.590273,4.808266,4.017233,3.927117,5.061803,5.856605,6.472635,9.297385,6.838650,5.374219,4.641721,4.048625,3.688632</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>3.703358134636017</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>112.671333,112.541954,112.519447,112.501617,112.480171,112.507729,112.627769,112.589890,112.613007,112.535782,112.499390,112.460365,112.634819,112.570984,112.610603,112.520454,112.576073,112.355339,112.425179,112.477814,112.384171,112.392929,112.212700,112.290840</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>111.952209,111.714233,111.495110,111.470863,111.351036,111.276176,111.214386,111.213593,111.212090,111.040108,110.992744,110.893326,110.889915,110.798561,110.805367,110.614540,110.605461,110.411453,110.236740,110.331696,110.142059,110.075180,110.043686,110.067162</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:48</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>108.742661,108.710289,108.668564,108.680832,108.664604,108.659584,108.648720,108.638458,108.688103,108.638092,108.611496,108.722450,108.717346,108.638832,108.658569,108.638222,108.623138,108.585655,108.570244,108.639008,108.626465,108.572762,108.592239,108.636467</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>108.913383,108.926956,108.639580,108.750053,108.698952,108.706459,108.830139,108.674431,108.867851,108.721886,108.740517,108.796844,108.982109,108.923462,108.840576,108.699623,108.788994,108.796494,108.730484,108.711884,108.763367,108.525879,108.761902,108.687660</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>107.328712,107.010361,106.655937,106.471382,106.183418,106.052330,105.902451,105.711288,105.596489,105.353668,105.221153,105.200844,105.068390,104.882500,104.828728,104.575684,104.531754,104.312828,103.949814,103.984612,103.874153,103.817406,103.760750,103.710030</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>107.932549,107.628212,107.361504,107.251274,107.108475,106.967377,106.838799,106.721031,106.749779,106.573044,106.390671,106.461472,106.361290,106.247673,106.267670,106.066628,106.013657,105.782066,105.711151,105.775467,105.694389,105.549637,105.613678,105.667679</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>108.6364669799805</v>
+      </c>
+      <c r="G87" t="n">
+        <v>108.1500015258789</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.4864654541015909</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.4498062387777091</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.268014987286552</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:27</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>108.1653442382812</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>108.742661,108.710289,108.668564,108.680832,108.664604,108.659584,108.648720,108.638458,108.688103,108.638092,108.611496,108.722450,108.717346,108.638832,108.658569,108.638222,108.623138,108.585655,108.570244,108.639008,108.626465,108.572762,108.592239,108.636467</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>108.459999,107.529999,106.900002,106.389999,106.050003,106.559998,106.660004,107.419998,107.260002,107.449997,107.040001,107.739998,107.400002,107.019997,107.010002,106.919998,106.730003,107.330002,107.320000,107.629997,107.730003,108.150002,108.150002,108.150002</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.282662,1.180290,1.768562,2.290833,2.614601,2.099586,1.988716,1.218460,1.428101,1.188095,1.571495,0.982452,1.317344,1.618835,1.648567,1.718224,1.893135,1.255653,1.250244,1.009011,0.896462,0.422760,0.442237,0.486465</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.260614,1.097638,1.654408,2.153241,2.465442,1.970333,1.864538,1.134295,1.331438,1.105719,1.468138,0.911873,1.226578,1.512648,1.540573,1.607018,1.773761,1.169900,1.164969,0.937481,0.832137,0.390902,0.408911,0.449806</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1.268014987286552</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>108.913383,108.926956,108.639580,108.750053,108.698952,108.706459,108.830139,108.674431,108.867851,108.721886,108.740517,108.796844,108.982109,108.923462,108.840576,108.699623,108.788994,108.796494,108.730484,108.711884,108.763367,108.525879,108.761902,108.687660</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>107.932549,107.628212,107.361504,107.251274,107.108475,106.967377,106.838799,106.721031,106.749779,106.573044,106.390671,106.461472,106.361290,106.247673,106.267670,106.066628,106.013657,105.782066,105.711151,105.775467,105.694389,105.549637,105.613678,105.667679</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:27</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>108.207863,108.215912,108.218483,108.236275,108.220474,108.209259,108.180939,108.183670,108.214203,108.111877,108.058876,108.138939,108.222855,108.200409,108.173363,108.220642,108.175629,108.149704,108.161530,108.248955,108.217567,108.173645,108.137436,108.165344</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>108.274345,108.378555,108.157341,108.212692,108.150688,108.156631,108.316460,108.267883,108.328407,108.207512,108.084824,108.266212,108.413879,108.385178,108.392250,108.342728,108.428047,108.331490,108.325493,108.390144,108.386368,108.099930,108.268661,108.284767</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>107.301880,107.122482,106.867393,106.780792,106.573257,106.439026,106.318779,106.201271,106.090179,105.825874,105.710785,105.694374,105.570724,105.383118,105.340790,105.174965,105.096878,105.002380,104.677757,104.743759,104.590164,104.530891,104.372910,104.256157</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>107.665375,107.479317,107.308716,107.258812,107.197632,107.057350,106.961601,106.896667,106.913010,106.688637,106.540741,106.583603,106.534821,106.371582,106.408218,106.303604,106.178955,106.023491,106.012871,106.110695,105.961487,105.843781,105.811882,105.782707</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>108.1653442382812</v>
+      </c>
+      <c r="G88" t="n">
+        <v>102.6900024414062</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.475341796874943</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5.331913201578812</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3.126024309414957</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:02</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>102.4702377319336</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>108.207863,108.215912,108.218483,108.236275,108.220474,108.209259,108.180939,108.183670,108.214203,108.111877,108.058876,108.138939,108.222855,108.200409,108.173363,108.220642,108.175629,108.149704,108.161530,108.248955,108.217567,108.173645,108.137436,108.165344</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>107.080002,107.059998,107.370003,106.910004,106.500000,107.089996,107.070000,105.339996,104.820000,104.290001,103.750000,104.849998,104.279999,104.230003,104.080002,103.980003,104.610001,104.419998,104.160004,104.220001,103.870003,103.190002,102.370003,102.690002</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.127861,1.155914,0.848480,1.326271,1.720474,1.119263,1.110939,2.843674,3.394203,3.821876,4.308876,3.288941,3.942856,3.970406,4.093361,4.240639,3.565628,3.729706,4.001526,4.028954,4.347564,4.983643,5.767433,5.475342</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1.053288,1.079688,0.790240,1.240549,1.615469,1.045161,1.037582,2.699519,3.238126,3.664662,4.153133,3.136806,3.781028,3.809273,3.932899,4.078321,3.408497,3.571831,3.841711,3.865816,4.185582,4.829579,5.633909,5.331913</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3.126024309414957</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>108.274345,108.378555,108.157341,108.212692,108.150688,108.156631,108.316460,108.267883,108.328407,108.207512,108.084824,108.266212,108.413879,108.385178,108.392250,108.342728,108.428047,108.331490,108.325493,108.390144,108.386368,108.099930,108.268661,108.284767</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>107.665375,107.479317,107.308716,107.258812,107.197632,107.057350,106.961601,106.896667,106.913010,106.688637,106.540741,106.583603,106.534821,106.371582,106.408218,106.303604,106.178955,106.023491,106.012871,106.110695,105.961487,105.843781,105.811882,105.782707</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:02</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>102.842560,102.773720,102.652077,102.588806,102.579620,102.535484,102.509270,102.465271,102.419914,102.411316,102.346725,102.365150,102.420639,102.483841,102.476395,102.502357,102.438972,102.505836,102.493118,102.576492,102.528542,102.539116,102.418648,102.470238</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>102.909966,102.954704,102.582985,102.716766,102.662193,102.587257,102.734489,102.458755,102.710732,102.636078,102.427513,102.685966,102.695824,102.771950,102.812515,102.722435,102.833168,102.927322,102.780785,102.870697,102.844551,102.571129,102.794495,102.800392</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>101.902969,101.635559,101.229836,101.045761,100.807663,100.685135,100.622169,100.447960,100.271690,100.095024,99.957558,99.930206,99.760330,99.678513,99.713966,99.587372,99.449402,99.377419,99.122726,99.196182,98.965996,99.033363,98.869209,98.709534</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>102.248123,101.999466,101.721825,101.537621,101.467453,101.374886,101.283524,101.135208,101.119064,100.984985,100.788116,100.832626,100.724426,100.668037,100.795822,100.657188,100.483452,100.389847,100.448196,100.498329,100.345261,100.330673,100.213943,100.255486</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>102.4702377319336</v>
+      </c>
+      <c r="G89" t="n">
+        <v>105.1600036621094</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.689765930175781</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.557784173171289</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.051199167455749</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:36</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>104.5718383789062</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>102.842560,102.773720,102.652077,102.588806,102.579620,102.535484,102.509270,102.465271,102.419914,102.411316,102.346725,102.365150,102.420639,102.483841,102.476395,102.502357,102.438972,102.505836,102.493118,102.576492,102.528542,102.539116,102.418648,102.470238</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>101.339996,102.010002,103.150002,103.190002,103.040001,102.260002,102.070000,101.570000,101.430000,104.730003,105.989998,105.489998,105.809998,105.849998,105.940002,105.550003,105.919998,105.720001,105.269997,105.440002,105.000000,105.209999,105.199997,105.160004</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.502564,0.763718,0.497925,0.601196,0.460381,0.275482,0.439270,0.895271,0.989914,2.318687,3.643273,3.124848,3.389359,3.366157,3.463607,3.047646,3.481026,3.214165,2.776879,2.863510,2.471458,2.670883,2.781349,2.689766</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1.482696,0.748670,0.482719,0.582611,0.446798,0.269394,0.430362,0.881433,0.975957,2.213967,3.437374,2.962222,3.203250,3.180120,3.269405,2.887396,3.286467,3.040262,2.637863,2.715772,2.353770,2.538621,2.643868,2.557784</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>2.051199167455749</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>102.909966,102.954704,102.582985,102.716766,102.662193,102.587257,102.734489,102.458755,102.710732,102.636078,102.427513,102.685966,102.695824,102.771950,102.812515,102.722435,102.833168,102.927322,102.780785,102.870697,102.844551,102.571129,102.794495,102.800392</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>102.248123,101.999466,101.721825,101.537621,101.467453,101.374886,101.283524,101.135208,101.119064,100.984985,100.788116,100.832626,100.724426,100.668037,100.795822,100.657188,100.483452,100.389847,100.448196,100.498329,100.345261,100.330673,100.213943,100.255486</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:36</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>105.126915,105.112808,105.022644,104.968513,105.002991,104.990410,104.927025,104.934364,104.917557,104.896103,104.848946,104.860703,104.867050,104.871155,104.862816,104.882195,104.802528,104.755470,104.774734,104.723236,104.710197,104.602142,104.525963,104.571838</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>105.242683,105.129974,104.938614,105.037971,104.999786,104.977882,104.983971,104.994370,105.104721,104.946648,104.880035,104.966560,105.003433,104.933685,105.062698,105.009705,104.978638,104.844437,104.862404,104.780151,104.707207,104.754539,104.707573,104.670242</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>104.028152,103.747871,103.309242,103.127419,102.948570,102.845322,102.683784,102.588921,102.430069,102.261246,102.180389,102.127548,101.893166,101.867958,101.781967,101.655441,101.415810,101.278847,100.984467,100.901627,100.803902,100.671341,100.480316,100.338310</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>104.448112,104.254822,103.900993,103.767609,103.706253,103.609779,103.507698,103.464569,103.436638,103.298790,103.152649,103.161865,103.028404,102.923157,102.984222,102.903702,102.628311,102.462677,102.479919,102.383011,102.293694,102.120331,102.013893,102.043587</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>104.5718383789062</v>
+      </c>
+      <c r="G90" t="n">
+        <v>104.7300033569336</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.1581649780274006</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.1510216489618105</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8794892049370004</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:44</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>104.4198150634766</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>105.126915,105.112808,105.022644,104.968513,105.002991,104.990410,104.927025,104.934364,104.917557,104.896103,104.848946,104.860703,104.867050,104.871155,104.862816,104.882195,104.802528,104.755470,104.774734,104.723236,104.710197,104.602142,104.525963,104.571838</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>105.830002,106.209999,106.230003,106.699997,106.169998,106.639999,106.470001,105.519997,105.589996,105.529999,103.650002,103.900002,103.559998,102.940002,103.400002,103.919998,104.059998,104.269997,104.320000,104.230003,104.169998,104.440002,104.830002,104.730003</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.703087,1.097191,1.207359,1.731484,1.167007,1.649589,1.542976,0.585633,0.672439,0.633896,1.198944,0.960701,1.307052,1.931153,1.462814,0.962197,0.742530,0.485473,0.454734,0.493233,0.540199,0.162140,0.304039,0.158165</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.664355,1.033039,1.136552,1.622759,1.099187,1.546877,1.449212,0.554997,0.636840,0.600678,1.156724,0.924640,1.262121,1.875998,1.414714,0.925902,0.713560,0.465593,0.435903,0.473216,0.518574,0.155247,0.290030,0.151022</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8794892049370004</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>105.242683,105.129974,104.938614,105.037971,104.999786,104.977882,104.983971,104.994370,105.104721,104.946648,104.880035,104.966560,105.003433,104.933685,105.062698,105.009705,104.978638,104.844437,104.862404,104.780151,104.707207,104.754539,104.707573,104.670242</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>104.448112,104.254822,103.900993,103.767609,103.706253,103.609779,103.507698,103.464569,103.436638,103.298790,103.152649,103.161865,103.028404,102.923157,102.984222,102.903702,102.628311,102.462677,102.479919,102.383011,102.293694,102.120331,102.013893,102.043587</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:44</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>104.676010,104.674141,104.642319,104.602676,104.646812,104.612556,104.505920,104.535065,104.527267,104.463303,104.492035,104.465141,104.437256,104.410568,104.414948,104.406410,104.396706,104.434319,104.419868,104.406242,104.424461,104.370804,104.333878,104.419815</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>104.779617,104.625847,104.633904,104.766518,104.641121,104.618622,104.579834,104.611671,104.636009,104.516197,104.492958,104.517838,104.596191,104.537430,104.516647,104.603790,104.620834,104.445770,104.426079,104.666817,104.470146,104.543427,104.398911,104.588051</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>103.782570,103.519913,103.235023,103.087883,102.941139,102.835983,102.629700,102.534454,102.370552,102.184128,102.137100,102.012993,101.872887,101.778526,101.679047,101.555054,101.322739,101.331520,100.944267,100.900597,100.813454,100.753113,100.655495,100.612785</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>104.148354,104.007645,103.742874,103.657341,103.569519,103.488281,103.342354,103.318893,103.283501,103.068825,103.004227,102.941475,102.836792,102.728622,102.761223,102.718918,102.517563,102.473427,102.384697,102.293571,102.228516,102.118431,102.032516,102.084106</t>
         </is>
       </c>
     </row>
